--- a/results/journals2025.xlsx
+++ b/results/journals2025.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11114"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aydin/sync/habil/submitted/32.radRetraction/radRetraction/results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294C724F-3719-9A4B-A0B0-5B2AFB507D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2440" yWindow="1620" windowWidth="21720" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -106,63 +100,69 @@
     <t>Discover oncology</t>
   </si>
   <si>
+    <t>The British journal of radiology</t>
+  </si>
+  <si>
+    <t>PloS one</t>
+  </si>
+  <si>
+    <t>Japanese journal of radiology</t>
+  </si>
+  <si>
+    <t>Computers in biology and medicine</t>
+  </si>
+  <si>
     <t>Acta radiologica (Stockholm, Sweden : 1987)</t>
   </si>
   <si>
-    <t>Japanese journal of radiology</t>
-  </si>
-  <si>
-    <t>Computers in biology and medicine</t>
-  </si>
-  <si>
-    <t>The British journal of radiology</t>
-  </si>
-  <si>
-    <t>PloS one</t>
-  </si>
-  <si>
     <t>Frontiers in neurology</t>
   </si>
   <si>
+    <t>Annals of surgical oncology</t>
+  </si>
+  <si>
     <t>Journal for immunotherapy of cancer</t>
   </si>
   <si>
-    <t>Annals of surgical oncology</t>
+    <t>Bioengineering (Basel, Switzerland)</t>
+  </si>
+  <si>
+    <t>Clinical &amp; translational oncology : official publication of the Federation of</t>
+  </si>
+  <si>
+    <t>Current medical imaging</t>
   </si>
   <si>
     <t>AJNR. American journal of neuroradiology</t>
   </si>
   <si>
-    <t>Clinical &amp; translational oncology : official publication of the Federation of</t>
-  </si>
-  <si>
-    <t>Current medical imaging</t>
+    <t>Frontiers in immunology</t>
+  </si>
+  <si>
+    <t>Ultrasound in medicine &amp; biology</t>
+  </si>
+  <si>
+    <t>Neuroradiology</t>
   </si>
   <si>
     <t>European journal of radiology open</t>
   </si>
   <si>
-    <t>Frontiers in immunology</t>
-  </si>
-  <si>
-    <t>Bioengineering (Basel, Switzerland)</t>
-  </si>
-  <si>
-    <t>Neuroradiology</t>
-  </si>
-  <si>
-    <t>Ultrasound in medicine &amp; biology</t>
+    <t>Journal of translational medicine</t>
   </si>
   <si>
     <t>World neurosurgery</t>
   </si>
   <si>
-    <t>Journal of translational medicine</t>
-  </si>
-  <si>
     <t>European journal of surgical oncology : the journal of the European Society of</t>
   </si>
   <si>
+    <t>World journal of gastrointestinal oncology</t>
+  </si>
+  <si>
+    <t>Translational oncology</t>
+  </si>
+  <si>
     <t>International journal of cardiology</t>
   </si>
   <si>
@@ -172,199 +172,211 @@
     <t>Life (Basel, Switzerland)</t>
   </si>
   <si>
-    <t>World journal of gastrointestinal oncology</t>
-  </si>
-  <si>
     <t>Neurosurgical review</t>
   </si>
   <si>
-    <t>Translational oncology</t>
+    <t>Journal of hepatocellular carcinoma</t>
+  </si>
+  <si>
+    <t>Physica medica : PM : an international journal devoted to the applications of</t>
+  </si>
+  <si>
+    <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
+  </si>
+  <si>
+    <t>Journal of applied clinical medical physics</t>
+  </si>
+  <si>
+    <t>Seminars in nuclear medicine</t>
+  </si>
+  <si>
+    <t>Digital health</t>
+  </si>
+  <si>
+    <t>Clinical breast cancer</t>
+  </si>
+  <si>
+    <t>European spine journal : official publication of the European Spine Society, the</t>
+  </si>
+  <si>
+    <t>Journal of medical imaging (Bellingham, Wash.)</t>
+  </si>
+  <si>
+    <t>AJR. American journal of roentgenology</t>
   </si>
   <si>
     <t>Clinical imaging</t>
   </si>
   <si>
-    <t>Journal of medical imaging (Bellingham, Wash.)</t>
-  </si>
-  <si>
-    <t>Clinical breast cancer</t>
-  </si>
-  <si>
-    <t>Journal of hepatocellular carcinoma</t>
-  </si>
-  <si>
-    <t>Digital health</t>
-  </si>
-  <si>
-    <t>Journal of applied clinical medical physics</t>
-  </si>
-  <si>
     <t>World journal of gastroenterology</t>
   </si>
   <si>
-    <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
-  </si>
-  <si>
-    <t>AJR. American journal of roentgenology</t>
-  </si>
-  <si>
-    <t>Seminars in nuclear medicine</t>
-  </si>
-  <si>
-    <t>Physica medica : PM : an international journal devoted to the applications of</t>
-  </si>
-  <si>
-    <t>European spine journal : official publication of the European Spine Society, the</t>
+    <t>Technology in cancer research &amp; treatment</t>
+  </si>
+  <si>
+    <t>IEEE journal of biomedical and health informatics</t>
   </si>
   <si>
     <t>Current oncology (Toronto, Ont.)</t>
   </si>
   <si>
+    <t>Nuclear medicine communications</t>
+  </si>
+  <si>
+    <t>NPJ precision oncology</t>
+  </si>
+  <si>
+    <t>Journal of ultrasound in medicine : official journal of the American Institute of</t>
+  </si>
+  <si>
+    <t>Radiotherapy and oncology : journal of the European Society for Therapeutic</t>
+  </si>
+  <si>
+    <t>Frontiers in endocrinology</t>
+  </si>
+  <si>
+    <t>European radiology experimental</t>
+  </si>
+  <si>
+    <t>BMC gastroenterology</t>
+  </si>
+  <si>
     <t>Journal of cancer research and clinical oncology</t>
   </si>
   <si>
-    <t>Frontiers in endocrinology</t>
-  </si>
-  <si>
-    <t>IEEE journal of biomedical and health informatics</t>
-  </si>
-  <si>
-    <t>European radiology experimental</t>
-  </si>
-  <si>
-    <t>BMC gastroenterology</t>
-  </si>
-  <si>
-    <t>NPJ precision oncology</t>
-  </si>
-  <si>
-    <t>Journal of ultrasound in medicine : official journal of the American Institute of</t>
-  </si>
-  <si>
-    <t>Nuclear medicine communications</t>
-  </si>
-  <si>
-    <t>Radiotherapy and oncology : journal of the European Society for Therapeutic</t>
-  </si>
-  <si>
-    <t>Technology in cancer research &amp; treatment</t>
+    <t>NPJ digital medicine</t>
+  </si>
+  <si>
+    <t>Molecular imaging and biology</t>
   </si>
   <si>
     <t>Journal of neuro-oncology</t>
   </si>
   <si>
-    <t>NPJ digital medicine</t>
+    <t>Ultrasound in obstetrics &amp; gynecology : the official journal of the International</t>
+  </si>
+  <si>
+    <t>Physics in medicine and biology</t>
+  </si>
+  <si>
+    <t>European journal of medical research</t>
+  </si>
+  <si>
+    <t>Radiology</t>
+  </si>
+  <si>
+    <t>Gland surgery</t>
+  </si>
+  <si>
+    <t>JCO clinical cancer informatics</t>
+  </si>
+  <si>
+    <t>Journal of personalized medicine</t>
+  </si>
+  <si>
+    <t>Journal of imaging</t>
+  </si>
+  <si>
+    <t>Heliyon</t>
+  </si>
+  <si>
+    <t>Dento maxillo facial radiology</t>
   </si>
   <si>
     <t>World journal of surgical oncology</t>
   </si>
   <si>
-    <t>Ultrasound in obstetrics &amp; gynecology : the official journal of the International</t>
-  </si>
-  <si>
-    <t>Physics in medicine and biology</t>
-  </si>
-  <si>
-    <t>Radiology</t>
-  </si>
-  <si>
-    <t>JCO clinical cancer informatics</t>
-  </si>
-  <si>
-    <t>Journal of imaging</t>
-  </si>
-  <si>
-    <t>Dento maxillo facial radiology</t>
-  </si>
-  <si>
-    <t>Molecular imaging and biology</t>
-  </si>
-  <si>
-    <t>Heliyon</t>
-  </si>
-  <si>
-    <t>European journal of medical research</t>
-  </si>
-  <si>
-    <t>Gland surgery</t>
-  </si>
-  <si>
-    <t>Journal of personalized medicine</t>
+    <t>Neuroscience</t>
+  </si>
+  <si>
+    <t>The international journal of cardiovascular imaging</t>
+  </si>
+  <si>
+    <t>Oral surgery, oral medicine, oral pathology and oral radiology</t>
+  </si>
+  <si>
+    <t>Biomedical physics &amp; engineering express</t>
+  </si>
+  <si>
+    <t>Journal of thoracic oncology : official publication of the International</t>
+  </si>
+  <si>
+    <t>iScience</t>
+  </si>
+  <si>
+    <t>Tomography (Ann Arbor, Mich.)</t>
+  </si>
+  <si>
+    <t>Medicine</t>
+  </si>
+  <si>
+    <t>Journal of thoracic imaging</t>
+  </si>
+  <si>
+    <t>International journal of general medicine</t>
+  </si>
+  <si>
+    <t>Nature communications</t>
+  </si>
+  <si>
+    <t>European heart journal. Cardiovascular Imaging</t>
+  </si>
+  <si>
+    <t>Translational cancer research</t>
+  </si>
+  <si>
+    <t>International journal of radiation oncology, biology, physics</t>
+  </si>
+  <si>
+    <t>NeuroImage</t>
+  </si>
+  <si>
+    <t>Biomedicines</t>
+  </si>
+  <si>
+    <t>Computerized medical imaging and graphics : the official journal of the</t>
+  </si>
+  <si>
+    <t>British journal of cancer</t>
+  </si>
+  <si>
+    <t>Journal of Cancer</t>
+  </si>
+  <si>
+    <t>Cancer letters</t>
+  </si>
+  <si>
+    <t>Magma (New York, N.Y.)</t>
+  </si>
+  <si>
+    <t>Medicina (Kaunas, Lithuania)</t>
+  </si>
+  <si>
+    <t>Journal of thoracic disease</t>
+  </si>
+  <si>
+    <t>Cancer biotherapy &amp; radiopharmaceuticals</t>
+  </si>
+  <si>
+    <t>Cureus</t>
+  </si>
+  <si>
+    <t>Neuro-oncology advances</t>
   </si>
   <si>
     <t>Neuro-oncology</t>
   </si>
   <si>
-    <t>Neuro-oncology advances</t>
-  </si>
-  <si>
-    <t>International journal of radiation oncology, biology, physics</t>
-  </si>
-  <si>
-    <t>Journal of thoracic disease</t>
-  </si>
-  <si>
-    <t>Biomedical physics &amp; engineering express</t>
-  </si>
-  <si>
-    <t>Cancer biotherapy &amp; radiopharmaceuticals</t>
-  </si>
-  <si>
-    <t>Biomedicines</t>
-  </si>
-  <si>
-    <t>Cureus</t>
-  </si>
-  <si>
-    <t>Journal of thoracic oncology : official publication of the International</t>
-  </si>
-  <si>
-    <t>Translational cancer research</t>
-  </si>
-  <si>
-    <t>NeuroImage</t>
-  </si>
-  <si>
-    <t>Medicina (Kaunas, Lithuania)</t>
-  </si>
-  <si>
-    <t>Medicine</t>
-  </si>
-  <si>
-    <t>British journal of cancer</t>
-  </si>
-  <si>
-    <t>iScience</t>
-  </si>
-  <si>
-    <t>Computerized medical imaging and graphics : the official journal of the</t>
-  </si>
-  <si>
-    <t>Oral surgery, oral medicine, oral pathology and oral radiology</t>
-  </si>
-  <si>
-    <t>Neuroscience</t>
-  </si>
-  <si>
-    <t>Nature communications</t>
-  </si>
-  <si>
-    <t>Tomography (Ann Arbor, Mich.)</t>
-  </si>
-  <si>
-    <t>Journal of Cancer</t>
-  </si>
-  <si>
-    <t>The international journal of cardiovascular imaging</t>
+    <t>Current opinion in urology</t>
+  </si>
+  <si>
+    <t>Artificial intelligence in medicine</t>
   </si>
   <si>
     <t>EJNMMI physics</t>
   </si>
   <si>
-    <t>European heart journal. Cardiovascular Imaging</t>
-  </si>
-  <si>
-    <t>Magma (New York, N.Y.)</t>
+    <t>Annals of nuclear medicine</t>
   </si>
   <si>
     <t>Medical &amp; biological engineering &amp; computing</t>
@@ -373,1325 +385,1307 @@
     <t>Pediatric radiology</t>
   </si>
   <si>
-    <t>Cancer letters</t>
-  </si>
-  <si>
-    <t>Current opinion in urology</t>
-  </si>
-  <si>
-    <t>Artificial intelligence in medicine</t>
-  </si>
-  <si>
-    <t>Annals of nuclear medicine</t>
-  </si>
-  <si>
-    <t>Journal of thoracic imaging</t>
-  </si>
-  <si>
-    <t>International journal of general medicine</t>
+    <t>British journal of hospital medicine (London, England : 2005)</t>
+  </si>
+  <si>
+    <t>Translational stroke research</t>
+  </si>
+  <si>
+    <t>Magnetic resonance in medicine</t>
+  </si>
+  <si>
+    <t>Brain sciences</t>
+  </si>
+  <si>
+    <t>Cancer medicine</t>
+  </si>
+  <si>
+    <t>Radiology. Imaging cancer</t>
+  </si>
+  <si>
+    <t>Future oncology (London, England)</t>
+  </si>
+  <si>
+    <t>International journal of computer assisted radiology and surgery</t>
+  </si>
+  <si>
+    <t>Clinical neuroradiology</t>
+  </si>
+  <si>
+    <t>Radiation oncology (London, England)</t>
+  </si>
+  <si>
+    <t>Journal of X-ray science and technology</t>
+  </si>
+  <si>
+    <t>Frontiers in aging neuroscience</t>
+  </si>
+  <si>
+    <t>Journal of the College of Physicians and Surgeons--Pakistan : JCPSP</t>
+  </si>
+  <si>
+    <t>Cancer management and research</t>
+  </si>
+  <si>
+    <t>Journal of endocrinological investigation</t>
+  </si>
+  <si>
+    <t>The oncologist</t>
+  </si>
+  <si>
+    <t>ArXiv</t>
+  </si>
+  <si>
+    <t>Oral radiology</t>
+  </si>
+  <si>
+    <t>medRxiv : the preprint server for health sciences</t>
+  </si>
+  <si>
+    <t>Medical image analysis</t>
+  </si>
+  <si>
+    <t>American journal of cancer research</t>
+  </si>
+  <si>
+    <t>Journal of medical Internet research</t>
+  </si>
+  <si>
+    <t>Neurological sciences : official journal of the Italian Neurological Society and</t>
+  </si>
+  <si>
+    <t>Acta neurochirurgica</t>
+  </si>
+  <si>
+    <t>American journal of translational research</t>
+  </si>
+  <si>
+    <t>EClinicalMedicine</t>
+  </si>
+  <si>
+    <t>BMC pregnancy and childbirth</t>
+  </si>
+  <si>
+    <t>Breast cancer research : BCR</t>
+  </si>
+  <si>
+    <t>Clinical cancer research : an official journal of the American Association for</t>
+  </si>
+  <si>
+    <t>NeuroImage. Clinical</t>
+  </si>
+  <si>
+    <t>Spine</t>
+  </si>
+  <si>
+    <t>International immunopharmacology</t>
+  </si>
+  <si>
+    <t>Respiratory research</t>
+  </si>
+  <si>
+    <t>Journal of bone oncology</t>
+  </si>
+  <si>
+    <t>Journal of multidisciplinary healthcare</t>
+  </si>
+  <si>
+    <t>RoFo : Fortschritte auf dem Gebiete der Rontgenstrahlen und der Nuklearmedizin</t>
+  </si>
+  <si>
+    <t>BMC musculoskeletal disorders</t>
+  </si>
+  <si>
+    <t>Cancer biomarkers : section A of Disease markers</t>
+  </si>
+  <si>
+    <t>Radiography (London, England : 1995)</t>
   </si>
   <si>
     <t>Oncology</t>
   </si>
   <si>
-    <t>Radiology. Imaging cancer</t>
-  </si>
-  <si>
-    <t>Translational stroke research</t>
-  </si>
-  <si>
-    <t>International journal of computer assisted radiology and surgery</t>
-  </si>
-  <si>
-    <t>Clinical neuroradiology</t>
-  </si>
-  <si>
-    <t>Radiation oncology (London, England)</t>
-  </si>
-  <si>
-    <t>RoFo : Fortschritte auf dem Gebiete der Rontgenstrahlen und der Nuklearmedizin</t>
-  </si>
-  <si>
-    <t>Cancer medicine</t>
-  </si>
-  <si>
-    <t>British journal of hospital medicine (London, England : 2005)</t>
-  </si>
-  <si>
-    <t>Journal of X-ray science and technology</t>
-  </si>
-  <si>
-    <t>Breast cancer research : BCR</t>
-  </si>
-  <si>
-    <t>BMC musculoskeletal disorders</t>
-  </si>
-  <si>
-    <t>Oral radiology</t>
-  </si>
-  <si>
-    <t>ArXiv</t>
-  </si>
-  <si>
-    <t>International immunopharmacology</t>
-  </si>
-  <si>
-    <t>medRxiv : the preprint server for health sciences</t>
-  </si>
-  <si>
-    <t>Journal of multidisciplinary healthcare</t>
-  </si>
-  <si>
-    <t>Medical image analysis</t>
-  </si>
-  <si>
-    <t>Cancer biomarkers : section A of Disease markers</t>
-  </si>
-  <si>
-    <t>BMC pregnancy and childbirth</t>
-  </si>
-  <si>
-    <t>Acta neurochirurgica</t>
-  </si>
-  <si>
-    <t>EClinicalMedicine</t>
-  </si>
-  <si>
-    <t>American journal of translational research</t>
-  </si>
-  <si>
-    <t>Neurological sciences : official journal of the Italian Neurological Society and</t>
-  </si>
-  <si>
-    <t>Frontiers in aging neuroscience</t>
-  </si>
-  <si>
-    <t>Clinical cancer research : an official journal of the American Association for</t>
-  </si>
-  <si>
-    <t>NeuroImage. Clinical</t>
+    <t>Journal of neurointerventional surgery</t>
   </si>
   <si>
     <t>Journal of ultrasound</t>
   </si>
   <si>
-    <t>Magnetic resonance in medicine</t>
-  </si>
-  <si>
-    <t>Brain sciences</t>
-  </si>
-  <si>
-    <t>Future oncology (London, England)</t>
-  </si>
-  <si>
-    <t>Spine</t>
-  </si>
-  <si>
-    <t>Respiratory research</t>
-  </si>
-  <si>
-    <t>Journal of medical Internet research</t>
-  </si>
-  <si>
-    <t>Journal of the College of Physicians and Surgeons--Pakistan : JCPSP</t>
-  </si>
-  <si>
-    <t>The oncologist</t>
-  </si>
-  <si>
-    <t>Journal of bone oncology</t>
-  </si>
-  <si>
-    <t>American journal of cancer research</t>
-  </si>
-  <si>
-    <t>Journal of endocrinological investigation</t>
-  </si>
-  <si>
-    <t>Radiography (London, England : 1995)</t>
-  </si>
-  <si>
-    <t>Cancer management and research</t>
-  </si>
-  <si>
-    <t>Journal of neurointerventional surgery</t>
+    <t>Radiology. Cardiothoracic imaging</t>
+  </si>
+  <si>
+    <t>Applied radiation and isotopes : including data, instrumentation and methods for</t>
+  </si>
+  <si>
+    <t>Journal of neurosurgery</t>
+  </si>
+  <si>
+    <t>Current urology</t>
+  </si>
+  <si>
+    <t>Multiple sclerosis and related disorders</t>
+  </si>
+  <si>
+    <t>Expert review of pharmacoeconomics &amp; outcomes research</t>
   </si>
   <si>
     <t>Echocardiography (Mount Kisco, N.Y.)</t>
   </si>
   <si>
-    <t>Current urology</t>
-  </si>
-  <si>
-    <t>Expert review of pharmacoeconomics &amp; outcomes research</t>
+    <t>Frontiers in neuroscience</t>
+  </si>
+  <si>
+    <t>World journal of radiology</t>
+  </si>
+  <si>
+    <t>Research square</t>
+  </si>
+  <si>
+    <t>Journal of medical radiation sciences</t>
+  </si>
+  <si>
+    <t>PeerJ</t>
+  </si>
+  <si>
+    <t>Diagnostic and interventional imaging</t>
+  </si>
+  <si>
+    <t>Circulation. Cardiovascular imaging</t>
+  </si>
+  <si>
+    <t>JACC. Advances</t>
+  </si>
+  <si>
+    <t>International journal of medical informatics</t>
+  </si>
+  <si>
+    <t>Cardiovascular and interventional radiology</t>
+  </si>
+  <si>
+    <t>Chinese journal of cancer research = Chung-kuo yen cheng yen chiu</t>
+  </si>
+  <si>
+    <t>Annals of medicine and surgery (2012)</t>
+  </si>
+  <si>
+    <t>European journal of vascular and endovascular surgery : the official journal of</t>
+  </si>
+  <si>
+    <t>Archivos de bronconeumologia</t>
+  </si>
+  <si>
+    <t>BMC medicine</t>
+  </si>
+  <si>
+    <t>Journal of hepatology</t>
+  </si>
+  <si>
+    <t>Ultrasonics</t>
+  </si>
+  <si>
+    <t>International journal of legal medicine</t>
+  </si>
+  <si>
+    <t>Clinical oncology (Royal College of Radiologists (Great Britain))</t>
+  </si>
+  <si>
+    <t>Journal of clinical ultrasound : JCU</t>
+  </si>
+  <si>
+    <t>Cancer cell international</t>
+  </si>
+  <si>
+    <t>European archives of oto-rhino-laryngology : official journal of the European</t>
+  </si>
+  <si>
+    <t>Biomedical engineering online</t>
+  </si>
+  <si>
+    <t>CNS neuroscience &amp; therapeutics</t>
+  </si>
+  <si>
+    <t>Scientific data</t>
+  </si>
+  <si>
+    <t>Cancer biology &amp; medicine</t>
+  </si>
+  <si>
+    <t>Revista da Associacao Medica Brasileira (1992)</t>
+  </si>
+  <si>
+    <t>Breathe (Sheffield, England)</t>
+  </si>
+  <si>
+    <t>Journal of clinical &amp; translational endocrinology</t>
+  </si>
+  <si>
+    <t>Clinical nuclear medicine</t>
+  </si>
+  <si>
+    <t>Breast cancer (Dove Medical Press)</t>
+  </si>
+  <si>
+    <t>Journal of dentistry</t>
+  </si>
+  <si>
+    <t>EJNMMI research</t>
+  </si>
+  <si>
+    <t>International journal of colorectal disease</t>
+  </si>
+  <si>
+    <t>Neurosurgery</t>
+  </si>
+  <si>
+    <t>Annals of the American Thoracic Society</t>
+  </si>
+  <si>
+    <t>Diagnostic and interventional radiology (Ankara, Turkey)</t>
+  </si>
+  <si>
+    <t>Journal of advanced research</t>
+  </si>
+  <si>
+    <t>EBioMedicine</t>
+  </si>
+  <si>
+    <t>PET clinics</t>
+  </si>
+  <si>
+    <t>Physics and imaging in radiation oncology</t>
+  </si>
+  <si>
+    <t>Children (Basel, Switzerland)</t>
+  </si>
+  <si>
+    <t>Clinical and molecular hepatology</t>
+  </si>
+  <si>
+    <t>World journal of clinical oncology</t>
+  </si>
+  <si>
+    <t>Orphanet journal of rare diseases</t>
+  </si>
+  <si>
+    <t>Frontiers in bioengineering and biotechnology</t>
+  </si>
+  <si>
+    <t>European journal of cancer (Oxford, England : 1990)</t>
+  </si>
+  <si>
+    <t>Journal of orthopaedic research : official publication of the Orthopaedic</t>
+  </si>
+  <si>
+    <t>Translational pediatrics</t>
+  </si>
+  <si>
+    <t>Strahlentherapie und Onkologie : Organ der Deutschen Rontgengesellschaft ... [et</t>
+  </si>
+  <si>
+    <t>Best practice &amp; research. Clinical endocrinology &amp; metabolism</t>
+  </si>
+  <si>
+    <t>Trends in cardiovascular medicine</t>
+  </si>
+  <si>
+    <t>Head &amp; neck</t>
+  </si>
+  <si>
+    <t>The Journal of thoracic and cardiovascular surgery</t>
+  </si>
+  <si>
+    <t>Expert review of anticancer therapy</t>
+  </si>
+  <si>
+    <t>Polish journal of radiology</t>
+  </si>
+  <si>
+    <t>Journal of stroke and cerebrovascular diseases : the official journal of National</t>
+  </si>
+  <si>
+    <t>Skeletal radiology</t>
+  </si>
+  <si>
+    <t>Journal of orthopaedic surgery and research</t>
+  </si>
+  <si>
+    <t>Journal of cancer research and therapeutics</t>
+  </si>
+  <si>
+    <t>Studies in health technology and informatics</t>
+  </si>
+  <si>
+    <t>Clinical lung cancer</t>
+  </si>
+  <si>
+    <t>World journal of clinical cases</t>
+  </si>
+  <si>
+    <t>Frontiers in cell and developmental biology</t>
   </si>
   <si>
     <t>Journal of cardiothoracic surgery</t>
   </si>
   <si>
-    <t>World journal of clinical oncology</t>
-  </si>
-  <si>
-    <t>Clinical nuclear medicine</t>
-  </si>
-  <si>
-    <t>Multiple sclerosis and related disorders</t>
-  </si>
-  <si>
-    <t>International journal of medical informatics</t>
-  </si>
-  <si>
-    <t>Journal of medical radiation sciences</t>
-  </si>
-  <si>
-    <t>Orphanet journal of rare diseases</t>
-  </si>
-  <si>
-    <t>Journal of neurosurgery</t>
-  </si>
-  <si>
-    <t>Breathe (Sheffield, England)</t>
-  </si>
-  <si>
-    <t>JACC. Advances</t>
-  </si>
-  <si>
-    <t>Circulation. Cardiovascular imaging</t>
-  </si>
-  <si>
-    <t>Frontiers in neuroscience</t>
-  </si>
-  <si>
-    <t>Frontiers in bioengineering and biotechnology</t>
-  </si>
-  <si>
-    <t>EJNMMI research</t>
-  </si>
-  <si>
-    <t>Radiology. Cardiothoracic imaging</t>
-  </si>
-  <si>
-    <t>Archivos de bronconeumologia</t>
-  </si>
-  <si>
-    <t>World journal of radiology</t>
-  </si>
-  <si>
-    <t>Chinese journal of cancer research = Chung-kuo yen cheng yen chiu</t>
-  </si>
-  <si>
-    <t>Journal of clinical &amp; translational endocrinology</t>
-  </si>
-  <si>
-    <t>Journal of advanced research</t>
-  </si>
-  <si>
-    <t>Revista da Associacao Medica Brasileira (1992)</t>
-  </si>
-  <si>
-    <t>EBioMedicine</t>
-  </si>
-  <si>
-    <t>Biomedical engineering online</t>
-  </si>
-  <si>
-    <t>European archives of oto-rhino-laryngology : official journal of the European</t>
-  </si>
-  <si>
-    <t>Cancer cell international</t>
-  </si>
-  <si>
-    <t>Journal of dentistry</t>
-  </si>
-  <si>
-    <t>Breast cancer (Dove Medical Press)</t>
-  </si>
-  <si>
-    <t>Children (Basel, Switzerland)</t>
-  </si>
-  <si>
-    <t>Cancer biology &amp; medicine</t>
-  </si>
-  <si>
-    <t>Scientific data</t>
-  </si>
-  <si>
-    <t>The Journal of thoracic and cardiovascular surgery</t>
-  </si>
-  <si>
-    <t>Neurosurgery</t>
-  </si>
-  <si>
-    <t>International journal of colorectal disease</t>
-  </si>
-  <si>
-    <t>European journal of cancer (Oxford, England : 1990)</t>
-  </si>
-  <si>
-    <t>Trends in cardiovascular medicine</t>
-  </si>
-  <si>
-    <t>Best practice &amp; research. Clinical endocrinology &amp; metabolism</t>
-  </si>
-  <si>
-    <t>Diagnostic and interventional radiology (Ankara, Turkey)</t>
-  </si>
-  <si>
-    <t>Strahlentherapie und Onkologie : Organ der Deutschen Rontgengesellschaft ... [et</t>
-  </si>
-  <si>
-    <t>Clinical and molecular hepatology</t>
-  </si>
-  <si>
-    <t>Annals of the American Thoracic Society</t>
-  </si>
-  <si>
-    <t>Journal of orthopaedic research : official publication of the Orthopaedic</t>
-  </si>
-  <si>
-    <t>PET clinics</t>
-  </si>
-  <si>
-    <t>CNS neuroscience &amp; therapeutics</t>
+    <t>The Laryngoscope</t>
+  </si>
+  <si>
+    <t>Clinical hemorheology and microcirculation</t>
   </si>
   <si>
     <t>Radiologie (Heidelberg, Germany)</t>
   </si>
   <si>
-    <t>Physics and imaging in radiation oncology</t>
-  </si>
-  <si>
-    <t>Cardiovascular and interventional radiology</t>
-  </si>
-  <si>
-    <t>Applied radiation and isotopes : including data, instrumentation and methods for</t>
-  </si>
-  <si>
-    <t>Research square</t>
-  </si>
-  <si>
-    <t>Frontiers in cell and developmental biology</t>
-  </si>
-  <si>
-    <t>International journal of legal medicine</t>
-  </si>
-  <si>
-    <t>Journal of clinical ultrasound : JCU</t>
-  </si>
-  <si>
-    <t>Journal of stroke and cerebrovascular diseases : the official journal of National</t>
-  </si>
-  <si>
-    <t>Studies in health technology and informatics</t>
-  </si>
-  <si>
-    <t>World journal of clinical cases</t>
-  </si>
-  <si>
-    <t>The Laryngoscope</t>
-  </si>
-  <si>
-    <t>BMC medicine</t>
-  </si>
-  <si>
-    <t>Journal of hepatology</t>
-  </si>
-  <si>
-    <t>European journal of vascular and endovascular surgery : the official journal of</t>
-  </si>
-  <si>
-    <t>Journal of orthopaedic surgery and research</t>
-  </si>
-  <si>
-    <t>Head &amp; neck</t>
-  </si>
-  <si>
-    <t>PeerJ</t>
-  </si>
-  <si>
-    <t>Annals of medicine and surgery (2012)</t>
-  </si>
-  <si>
-    <t>Journal of cancer research and therapeutics</t>
-  </si>
-  <si>
-    <t>Clinical oncology (Royal College of Radiologists (Great Britain))</t>
-  </si>
-  <si>
-    <t>Ultrasonics</t>
-  </si>
-  <si>
-    <t>Diagnostic and interventional imaging</t>
-  </si>
-  <si>
-    <t>Translational pediatrics</t>
-  </si>
-  <si>
-    <t>Expert review of anticancer therapy</t>
-  </si>
-  <si>
-    <t>Clinical hemorheology and microcirculation</t>
-  </si>
-  <si>
-    <t>Clinical lung cancer</t>
-  </si>
-  <si>
-    <t>Skeletal radiology</t>
-  </si>
-  <si>
-    <t>Polish journal of radiology</t>
+    <t>JACC. Cardiovascular imaging</t>
+  </si>
+  <si>
+    <t>PLoS computational biology</t>
+  </si>
+  <si>
+    <t>eLife</t>
+  </si>
+  <si>
+    <t>Archivos espanoles de urologia</t>
+  </si>
+  <si>
+    <t>International journal of molecular sciences</t>
+  </si>
+  <si>
+    <t>Brain topography</t>
+  </si>
+  <si>
+    <t>Zhonghua zhong liu za zhi [Chinese journal of oncology]</t>
+  </si>
+  <si>
+    <t>Aesthetic surgery journal</t>
+  </si>
+  <si>
+    <t>Ultrasonography (Seoul, Korea)</t>
+  </si>
+  <si>
+    <t>JAMA oncology</t>
+  </si>
+  <si>
+    <t>Biosensors</t>
+  </si>
+  <si>
+    <t>Oncology letters</t>
+  </si>
+  <si>
+    <t>International journal of particle therapy</t>
+  </si>
+  <si>
+    <t>Urologie (Heidelberg, Germany)</t>
+  </si>
+  <si>
+    <t>Advanced biology</t>
+  </si>
+  <si>
+    <t>Zhonghua jie he he hu xi za zhi = Zhonghua jiehe he huxi zazhi = Chinese journal</t>
+  </si>
+  <si>
+    <t>Radiographics : a review publication of the Radiological Society of North</t>
+  </si>
+  <si>
+    <t>Journal of nuclear medicine technology</t>
+  </si>
+  <si>
+    <t>Diabetes, metabolic syndrome and obesity : targets and therapy</t>
+  </si>
+  <si>
+    <t>Journal of breast imaging</t>
+  </si>
+  <si>
+    <t>Urologic oncology</t>
+  </si>
+  <si>
+    <t>Hernia : the journal of hernias and abdominal wall surgery</t>
+  </si>
+  <si>
+    <t>The Knee</t>
+  </si>
+  <si>
+    <t>Wiley interdisciplinary reviews. Nanomedicine and nanobiotechnology</t>
+  </si>
+  <si>
+    <t>Clinical physiology and functional imaging</t>
+  </si>
+  <si>
+    <t>Cerebellum (London, England)</t>
+  </si>
+  <si>
+    <t>Clinical epigenetics</t>
+  </si>
+  <si>
+    <t>Chinese medical journal</t>
+  </si>
+  <si>
+    <t>Urologia</t>
+  </si>
+  <si>
+    <t>Cancer cell</t>
+  </si>
+  <si>
+    <t>ESMO open</t>
+  </si>
+  <si>
+    <t>The European respiratory journal</t>
+  </si>
+  <si>
+    <t>Zhonghua xin xue guan bing za zhi</t>
+  </si>
+  <si>
+    <t>Seminars in ophthalmology</t>
+  </si>
+  <si>
+    <t>The Journal of infection</t>
+  </si>
+  <si>
+    <t>BJR open</t>
+  </si>
+  <si>
+    <t>Cancer radiotherapie : journal de la Societe francaise de radiotherapie</t>
+  </si>
+  <si>
+    <t>Journal of clinical neuroscience : official journal of the Neurosurgical Society</t>
+  </si>
+  <si>
+    <t>The neurologist</t>
+  </si>
+  <si>
+    <t>JAMA surgery</t>
+  </si>
+  <si>
+    <t>Frontiers in public health</t>
+  </si>
+  <si>
+    <t>Journal of medical imaging and radiation sciences</t>
+  </si>
+  <si>
+    <t>Gastrointestinal endoscopy clinics of North America</t>
+  </si>
+  <si>
+    <t>Clinical neurophysiology : official journal of the International Federation of</t>
+  </si>
+  <si>
+    <t>Placenta</t>
+  </si>
+  <si>
+    <t>American journal of rhinology &amp; allergy</t>
+  </si>
+  <si>
+    <t>Therapeutic advances in neurological disorders</t>
+  </si>
+  <si>
+    <t>British journal of sports medicine</t>
+  </si>
+  <si>
+    <t>Radiology and oncology</t>
+  </si>
+  <si>
+    <t>Acta medica Okayama</t>
+  </si>
+  <si>
+    <t>Annals of medicine</t>
+  </si>
+  <si>
+    <t>The EPMA journal</t>
+  </si>
+  <si>
+    <t>Epilepsy &amp; behavior : E&amp;B</t>
+  </si>
+  <si>
+    <t>Neurotherapeutics : the journal of the American Society for Experimental</t>
+  </si>
+  <si>
+    <t>Cancer science</t>
+  </si>
+  <si>
+    <t>International journal of hyperthermia : the official journal of European Society</t>
+  </si>
+  <si>
+    <t>Research (Washington, D.C.)</t>
+  </si>
+  <si>
+    <t>Journal of vascular and interventional radiology : JVIR</t>
+  </si>
+  <si>
+    <t>Clinics (Sao Paulo, Brazil)</t>
+  </si>
+  <si>
+    <t>Hellenic journal of cardiology : HJC = Hellenike kardiologike epitheorese</t>
+  </si>
+  <si>
+    <t>Neurology and therapy</t>
+  </si>
+  <si>
+    <t>Rheumatology (Oxford, England)</t>
+  </si>
+  <si>
+    <t>Endocrine</t>
+  </si>
+  <si>
+    <t>Annals of neurology</t>
+  </si>
+  <si>
+    <t>Cancer genetics</t>
+  </si>
+  <si>
+    <t>Frontiers in veterinary science</t>
+  </si>
+  <si>
+    <t>Journal of biomedical physics &amp; engineering</t>
+  </si>
+  <si>
+    <t>Frontiers in medical technology</t>
+  </si>
+  <si>
+    <t>Discovery medicine</t>
+  </si>
+  <si>
+    <t>Clinical oral investigations</t>
+  </si>
+  <si>
+    <t>Clinical proteomics</t>
+  </si>
+  <si>
+    <t>Rheumatology international</t>
+  </si>
+  <si>
+    <t>Frontiers in cardiovascular medicine</t>
+  </si>
+  <si>
+    <t>European journal of ophthalmology</t>
+  </si>
+  <si>
+    <t>Journal of pain research</t>
+  </si>
+  <si>
+    <t>Ultrasonic imaging</t>
+  </si>
+  <si>
+    <t>Journal of gastroenterology and hepatology</t>
+  </si>
+  <si>
+    <t>United European gastroenterology journal</t>
+  </si>
+  <si>
+    <t>Advances in radiation oncology</t>
+  </si>
+  <si>
+    <t>American journal of otolaryngology</t>
+  </si>
+  <si>
+    <t>Tzu chi medical journal</t>
+  </si>
+  <si>
+    <t>Journal of critical care</t>
+  </si>
+  <si>
+    <t>European journal of obstetrics &amp; gynecology and reproductive biology: X</t>
+  </si>
+  <si>
+    <t>Health information science and systems</t>
+  </si>
+  <si>
+    <t>Health science reports</t>
+  </si>
+  <si>
+    <t>Kidney &amp; blood pressure research</t>
+  </si>
+  <si>
+    <t>Nature reviews. Cardiology</t>
+  </si>
+  <si>
+    <t>Journal of cardiovascular pharmacology</t>
+  </si>
+  <si>
+    <t>NMR in biomedicine</t>
+  </si>
+  <si>
+    <t>Gastrointestinal endoscopy</t>
+  </si>
+  <si>
+    <t>Oncoimmunology</t>
+  </si>
+  <si>
+    <t>Digestive diseases and sciences</t>
+  </si>
+  <si>
+    <t>Legal medicine (Tokyo, Japan)</t>
+  </si>
+  <si>
+    <t>Annals of hematology</t>
+  </si>
+  <si>
+    <t>Radiological physics and technology</t>
+  </si>
+  <si>
+    <t>Journal of inflammation research</t>
+  </si>
+  <si>
+    <t>Human brain mapping</t>
+  </si>
+  <si>
+    <t>Clinical and translational gastroenterology</t>
+  </si>
+  <si>
+    <t>Photoacoustics</t>
+  </si>
+  <si>
+    <t>Physical and engineering sciences in medicine</t>
+  </si>
+  <si>
+    <t>Neuroinformatics</t>
+  </si>
+  <si>
+    <t>BMC infectious diseases</t>
+  </si>
+  <si>
+    <t>Hematology/oncology clinics of North America</t>
+  </si>
+  <si>
+    <t>Brain and behavior</t>
+  </si>
+  <si>
+    <t>International urology and nephrology</t>
+  </si>
+  <si>
+    <t>The neuroradiology journal</t>
+  </si>
+  <si>
+    <t>Clinical and translational medicine</t>
+  </si>
+  <si>
+    <t>Journal of the anus, rectum and colon</t>
+  </si>
+  <si>
+    <t>Cartilage</t>
+  </si>
+  <si>
+    <t>Frontiers in surgery</t>
+  </si>
+  <si>
+    <t>IEEE transactions on bio-medical engineering</t>
+  </si>
+  <si>
+    <t>Journal of dental research</t>
+  </si>
+  <si>
+    <t>Nuklearmedizin. Nuclear medicine</t>
+  </si>
+  <si>
+    <t>Journal of medical systems</t>
+  </si>
+  <si>
+    <t>Surgical endoscopy</t>
+  </si>
+  <si>
+    <t>Molecular carcinogenesis</t>
+  </si>
+  <si>
+    <t>International journal of radiation biology</t>
+  </si>
+  <si>
+    <t>Cerebral cortex (New York, N.Y. : 1991)</t>
+  </si>
+  <si>
+    <t>Naunyn-Schmiedeberg's archives of pharmacology</t>
+  </si>
+  <si>
+    <t>Journal of oral pathology &amp; medicine : official publication of the International</t>
+  </si>
+  <si>
+    <t>Revista espanola de medicina nuclear e imagen molecular</t>
+  </si>
+  <si>
+    <t>Neurocritical care</t>
+  </si>
+  <si>
+    <t>Advanced materials (Deerfield Beach, Fla.)</t>
+  </si>
+  <si>
+    <t>International journal of urology : official journal of the Japanese Urological</t>
+  </si>
+  <si>
+    <t>Communications medicine</t>
+  </si>
+  <si>
+    <t>Visceral medicine</t>
+  </si>
+  <si>
+    <t>Clinical cardiology</t>
+  </si>
+  <si>
+    <t>Methods in cell biology</t>
+  </si>
+  <si>
+    <t>Learning health systems</t>
+  </si>
+  <si>
+    <t>BMC medical informatics and decision making</t>
+  </si>
+  <si>
+    <t>Radiology. Artificial intelligence</t>
+  </si>
+  <si>
+    <t>BMJ (Clinical research ed.)</t>
+  </si>
+  <si>
+    <t>Frontiers in dental medicine</t>
+  </si>
+  <si>
+    <t>Cellular oncology (Dordrecht, Netherlands)</t>
+  </si>
+  <si>
+    <t>Archives of gynecology and obstetrics</t>
+  </si>
+  <si>
+    <t>Journal of maxillofacial and oral surgery</t>
+  </si>
+  <si>
+    <t>Annals of clinical and translational neurology</t>
+  </si>
+  <si>
+    <t>Journal of Korean Neurosurgical Society</t>
+  </si>
+  <si>
+    <t>Canadian Urological Association journal = Journal de l'Association des urologues</t>
+  </si>
+  <si>
+    <t>Frontiers in sports and active living</t>
+  </si>
+  <si>
+    <t>bioRxiv : the preprint server for biology</t>
+  </si>
+  <si>
+    <t>Tumori</t>
+  </si>
+  <si>
+    <t>Cancer metastasis reviews</t>
   </si>
   <si>
     <t>Nutrition, metabolism, and cardiovascular diseases : NMCD</t>
   </si>
   <si>
-    <t>PLoS computational biology</t>
-  </si>
-  <si>
-    <t>Wiley interdisciplinary reviews. Nanomedicine and nanobiotechnology</t>
+    <t>Cancer prevention research (Philadelphia, Pa.)</t>
+  </si>
+  <si>
+    <t>Philosophical transactions. Series A, Mathematical, physical, and engineering</t>
+  </si>
+  <si>
+    <t>Statistics in medicine</t>
+  </si>
+  <si>
+    <t>Veterinary and comparative oncology</t>
+  </si>
+  <si>
+    <t>Techniques in coloproctology</t>
+  </si>
+  <si>
+    <t>Gynecologic and obstetric investigation</t>
+  </si>
+  <si>
+    <t>Science progress</t>
+  </si>
+  <si>
+    <t>Molecular biomedicine</t>
+  </si>
+  <si>
+    <t>EJNMMI reports</t>
+  </si>
+  <si>
+    <t>Pancreatology : official journal of the International Association of</t>
+  </si>
+  <si>
+    <t>European urology</t>
+  </si>
+  <si>
+    <t>Haematologica</t>
+  </si>
+  <si>
+    <t>Circulation research</t>
+  </si>
+  <si>
+    <t>International journal of women's health</t>
+  </si>
+  <si>
+    <t>Biomedical reports</t>
+  </si>
+  <si>
+    <t>Gastroenterology report</t>
+  </si>
+  <si>
+    <t>Chinese neurosurgical journal</t>
+  </si>
+  <si>
+    <t>Clinical &amp; experimental metastasis</t>
+  </si>
+  <si>
+    <t>JAMA cardiology</t>
+  </si>
+  <si>
+    <t>Healthcare (Basel, Switzerland)</t>
+  </si>
+  <si>
+    <t>BMC surgery</t>
+  </si>
+  <si>
+    <t>Frontiers in genetics</t>
+  </si>
+  <si>
+    <t>Acta obstetricia et gynecologica Scandinavica</t>
+  </si>
+  <si>
+    <t>Biochimica et biophysica acta. Reviews on cancer</t>
+  </si>
+  <si>
+    <t>Proceedings of SPIE--the International Society for Optical Engineering</t>
+  </si>
+  <si>
+    <t>Cancer discovery</t>
+  </si>
+  <si>
+    <t>BJR artificial intelligence</t>
+  </si>
+  <si>
+    <t>Anticancer research</t>
+  </si>
+  <si>
+    <t>The Journal of urology</t>
+  </si>
+  <si>
+    <t>IEEE transactions on neural networks and learning systems</t>
+  </si>
+  <si>
+    <t>Clinical and translational radiation oncology</t>
+  </si>
+  <si>
+    <t>European journal of pediatrics</t>
+  </si>
+  <si>
+    <t>World journal of hepatology</t>
+  </si>
+  <si>
+    <t>Acta cardiologica</t>
+  </si>
+  <si>
+    <t>Global spine journal</t>
+  </si>
+  <si>
+    <t>Journal of global antimicrobial resistance</t>
+  </si>
+  <si>
+    <t>The Journal of craniofacial surgery</t>
+  </si>
+  <si>
+    <t>Canadian Association of Radiologists journal = Journal l'Association canadienne</t>
+  </si>
+  <si>
+    <t>Hepatology research : the official journal of the Japan Society of Hepatology</t>
+  </si>
+  <si>
+    <t>International journal of chronic obstructive pulmonary disease</t>
+  </si>
+  <si>
+    <t>Medical ultrasonography</t>
+  </si>
+  <si>
+    <t>Frontiers in pharmacology</t>
+  </si>
+  <si>
+    <t>Research in diagnostic and interventional imaging</t>
+  </si>
+  <si>
+    <t>Journal of affective disorders</t>
+  </si>
+  <si>
+    <t>Heart and vessels</t>
+  </si>
+  <si>
+    <t>Alzheimer's &amp; dementia : the journal of the Alzheimer's Association</t>
+  </si>
+  <si>
+    <t>Current problems in cancer</t>
+  </si>
+  <si>
+    <t>Journal of gastrointestinal surgery : official journal of the Society for Surgery</t>
+  </si>
+  <si>
+    <t>International endodontic journal</t>
+  </si>
+  <si>
+    <t>Journal of gynecologic oncology</t>
+  </si>
+  <si>
+    <t>Cerebrovascular diseases (Basel, Switzerland)</t>
+  </si>
+  <si>
+    <t>Digestive and liver disease : official journal of the Italian Society of</t>
+  </si>
+  <si>
+    <t>Cardiology journal</t>
+  </si>
+  <si>
+    <t>Coronary artery disease</t>
+  </si>
+  <si>
+    <t>European urology oncology</t>
+  </si>
+  <si>
+    <t>DEN open</t>
+  </si>
+  <si>
+    <t>Current opinion in cardiology</t>
+  </si>
+  <si>
+    <t>BMJ open respiratory research</t>
+  </si>
+  <si>
+    <t>Annals of surgery</t>
+  </si>
+  <si>
+    <t>Biological psychiatry</t>
+  </si>
+  <si>
+    <t>American journal of veterinary research</t>
+  </si>
+  <si>
+    <t>Journal of neuroendocrinology</t>
+  </si>
+  <si>
+    <t>Journal of cardiovascular computed tomography</t>
+  </si>
+  <si>
+    <t>Cancer research and treatment</t>
+  </si>
+  <si>
+    <t>Veterinary sciences</t>
+  </si>
+  <si>
+    <t>Medical oncology (Northwood, London, England)</t>
+  </si>
+  <si>
+    <t>Journal of medical signals and sensors</t>
+  </si>
+  <si>
+    <t>Nuclear medicine and molecular imaging</t>
+  </si>
+  <si>
+    <t>The Journal of biological chemistry</t>
+  </si>
+  <si>
+    <t>Asian journal of psychiatry</t>
+  </si>
+  <si>
+    <t>BJS open</t>
+  </si>
+  <si>
+    <t>Breast cancer research and treatment</t>
+  </si>
+  <si>
+    <t>Translational andrology and urology</t>
+  </si>
+  <si>
+    <t>BMC cardiovascular disorders</t>
+  </si>
+  <si>
+    <t>Frontiers in pediatrics</t>
+  </si>
+  <si>
+    <t>American Society of Clinical Oncology educational book. American Society of</t>
+  </si>
+  <si>
+    <t>Zhonghua yi xue za zhi</t>
+  </si>
+  <si>
+    <t>Brain research</t>
+  </si>
+  <si>
+    <t>Neurogastroenterology and motility</t>
+  </si>
+  <si>
+    <t>Clinical rheumatology</t>
+  </si>
+  <si>
+    <t>The Lancet. Rheumatology</t>
+  </si>
+  <si>
+    <t>JMIR AI</t>
+  </si>
+  <si>
+    <t>African journal of reproductive health</t>
+  </si>
+  <si>
+    <t>International forum of allergy &amp; rhinology</t>
+  </si>
+  <si>
+    <t>The Lancet regional health. Western Pacific</t>
+  </si>
+  <si>
+    <t>Zhonghua wei chang wai ke za zhi = Chinese journal of gastrointestinal surgery</t>
+  </si>
+  <si>
+    <t>Seminars in cancer biology</t>
+  </si>
+  <si>
+    <t>Ginekologia polska</t>
+  </si>
+  <si>
+    <t>Journal of orthopaedic translation</t>
   </si>
   <si>
     <t>Journal of vascular surgery. Venous and lymphatic disorders</t>
   </si>
   <si>
-    <t>ESMO open</t>
-  </si>
-  <si>
-    <t>The European respiratory journal</t>
-  </si>
-  <si>
-    <t>Urologia</t>
-  </si>
-  <si>
-    <t>Journal of Korean Neurosurgical Society</t>
-  </si>
-  <si>
-    <t>Archivos espanoles de urologia</t>
-  </si>
-  <si>
-    <t>eLife</t>
-  </si>
-  <si>
-    <t>Oncoimmunology</t>
-  </si>
-  <si>
-    <t>International journal of radiation biology</t>
-  </si>
-  <si>
-    <t>Neurotherapeutics : the journal of the American Society for Experimental</t>
-  </si>
-  <si>
-    <t>Gastrointestinal endoscopy</t>
-  </si>
-  <si>
-    <t>Neurocritical care</t>
-  </si>
-  <si>
-    <t>Revista espanola de medicina nuclear e imagen molecular</t>
-  </si>
-  <si>
-    <t>Cancer science</t>
-  </si>
-  <si>
-    <t>Surgical endoscopy</t>
-  </si>
-  <si>
-    <t>Journal of vascular and interventional radiology : JVIR</t>
-  </si>
-  <si>
-    <t>Journal of medical systems</t>
-  </si>
-  <si>
-    <t>Ultrasonography (Seoul, Korea)</t>
-  </si>
-  <si>
-    <t>Zhonghua zhong liu za zhi [Chinese journal of oncology]</t>
-  </si>
-  <si>
-    <t>Endocrine</t>
-  </si>
-  <si>
-    <t>International journal of molecular sciences</t>
-  </si>
-  <si>
-    <t>IEEE transactions on bio-medical engineering</t>
-  </si>
-  <si>
-    <t>Cerebellum (London, England)</t>
-  </si>
-  <si>
-    <t>Clinical epigenetics</t>
-  </si>
-  <si>
-    <t>Physical and engineering sciences in medicine</t>
-  </si>
-  <si>
-    <t>Journal of gynecologic oncology</t>
-  </si>
-  <si>
-    <t>Radiology and oncology</t>
-  </si>
-  <si>
-    <t>International journal of particle therapy</t>
-  </si>
-  <si>
-    <t>Biosensors</t>
-  </si>
-  <si>
-    <t>BJR open</t>
-  </si>
-  <si>
-    <t>Coronary artery disease</t>
-  </si>
-  <si>
-    <t>European urology oncology</t>
-  </si>
-  <si>
-    <t>JAMA surgery</t>
-  </si>
-  <si>
-    <t>Acta medica Okayama</t>
-  </si>
-  <si>
-    <t>Hellenic journal of cardiology : HJC = Hellenike kardiologike epitheorese</t>
-  </si>
-  <si>
-    <t>Zhonghua xin xue guan bing za zhi</t>
-  </si>
-  <si>
-    <t>Annals of medicine</t>
-  </si>
-  <si>
-    <t>British journal of sports medicine</t>
-  </si>
-  <si>
-    <t>Therapeutic advances in neurological disorders</t>
-  </si>
-  <si>
-    <t>Placenta</t>
-  </si>
-  <si>
-    <t>Clinical neurophysiology : official journal of the International Federation of</t>
-  </si>
-  <si>
-    <t>Gastrointestinal endoscopy clinics of North America</t>
-  </si>
-  <si>
-    <t>DEN open</t>
-  </si>
-  <si>
-    <t>American journal of rhinology &amp; allergy</t>
-  </si>
-  <si>
-    <t>Cancer research and treatment</t>
-  </si>
-  <si>
-    <t>The EPMA journal</t>
-  </si>
-  <si>
-    <t>International journal of hyperthermia : the official journal of European Society</t>
-  </si>
-  <si>
-    <t>The Knee</t>
-  </si>
-  <si>
-    <t>Hernia : the journal of hernias and abdominal wall surgery</t>
-  </si>
-  <si>
-    <t>Diabetes, metabolic syndrome and obesity : targets and therapy</t>
-  </si>
-  <si>
-    <t>Advanced materials (Deerfield Beach, Fla.)</t>
-  </si>
-  <si>
-    <t>Discovery medicine..</t>
-  </si>
-  <si>
-    <t>Cerebrovascular diseases (Basel, Switzerland)</t>
-  </si>
-  <si>
-    <t>Frontiers in medical technology</t>
-  </si>
-  <si>
-    <t>Journal of biomedical physics &amp; engineering</t>
-  </si>
-  <si>
-    <t>Cancer genetics</t>
-  </si>
-  <si>
-    <t>Annals of neurology</t>
-  </si>
-  <si>
-    <t>Digestive and liver disease : official journal of the Italian Society of</t>
-  </si>
-  <si>
-    <t>Neurology and therapy</t>
-  </si>
-  <si>
-    <t>Clinical oral investigations</t>
-  </si>
-  <si>
-    <t>Clinics (Sao Paulo, Brazil)</t>
-  </si>
-  <si>
-    <t>Advances in radiation oncology</t>
-  </si>
-  <si>
-    <t>Seminars in ophthalmology</t>
-  </si>
-  <si>
-    <t>Journal of nuclear medicine technology</t>
-  </si>
-  <si>
-    <t>Communications medicine</t>
-  </si>
-  <si>
-    <t>Clinical cardiology</t>
-  </si>
-  <si>
-    <t>Alzheimer's &amp; dementia : the journal of the Alzheimer's Association</t>
-  </si>
-  <si>
-    <t>Current problems in cancer</t>
-  </si>
-  <si>
-    <t>Clinical proteomics</t>
-  </si>
-  <si>
-    <t>Methods in cell biology</t>
-  </si>
-  <si>
-    <t>Molecular carcinogenesis</t>
-  </si>
-  <si>
-    <t>Rheumatology international</t>
-  </si>
-  <si>
-    <t>Journal of gastrointestinal surgery : official journal of the Society for Surgery</t>
-  </si>
-  <si>
-    <t>Kidney &amp; blood pressure research</t>
-  </si>
-  <si>
-    <t>American journal of otolaryngology</t>
-  </si>
-  <si>
-    <t>Nature reviews. Cardiology</t>
-  </si>
-  <si>
-    <t>European journal of obstetrics &amp; gynecology and reproductive biology: X</t>
-  </si>
-  <si>
-    <t>Journal of critical care</t>
-  </si>
-  <si>
-    <t>Health science reports</t>
-  </si>
-  <si>
-    <t>Tzu chi medical journal</t>
-  </si>
-  <si>
-    <t>Health information science and systems</t>
-  </si>
-  <si>
-    <t>United European gastroenterology journal</t>
-  </si>
-  <si>
-    <t>Learning health systems</t>
-  </si>
-  <si>
-    <t>BMC medical informatics and decision making</t>
-  </si>
-  <si>
-    <t>Radiology. Artificial intelligence</t>
-  </si>
-  <si>
-    <t>Annals of hematology</t>
-  </si>
-  <si>
-    <t>American journal of veterinary research</t>
-  </si>
-  <si>
-    <t>Neuroinformatics</t>
-  </si>
-  <si>
-    <t>BMC infectious diseases</t>
-  </si>
-  <si>
-    <t>Clinical and translational gastroenterology</t>
-  </si>
-  <si>
-    <t>Journal of neuroendocrinology</t>
-  </si>
-  <si>
-    <t>Hematology/oncology clinics of North America</t>
-  </si>
-  <si>
-    <t>Clinical and translational medicine</t>
-  </si>
-  <si>
-    <t>Brain and behavior</t>
-  </si>
-  <si>
-    <t>International urology and nephrology</t>
-  </si>
-  <si>
-    <t>Journal of affective disorders</t>
-  </si>
-  <si>
-    <t>Journal of inflammation research</t>
-  </si>
-  <si>
-    <t>Heart and vessels</t>
-  </si>
-  <si>
-    <t>The neuroradiology journal</t>
-  </si>
-  <si>
-    <t>Radiological physics and technology</t>
-  </si>
-  <si>
-    <t>Human brain mapping</t>
-  </si>
-  <si>
-    <t>Ultrasonic imaging</t>
-  </si>
-  <si>
-    <t>International endodontic journal</t>
-  </si>
-  <si>
-    <t>Epilepsy &amp; behavior : E&amp;B</t>
-  </si>
-  <si>
-    <t>Journal of maxillofacial and oral surgery</t>
-  </si>
-  <si>
-    <t>Journal of breast imaging</t>
-  </si>
-  <si>
-    <t>Cancer metastasis reviews</t>
-  </si>
-  <si>
-    <t>Tumori</t>
-  </si>
-  <si>
-    <t>bioRxiv : the preprint server for biology</t>
-  </si>
-  <si>
-    <t>Frontiers in sports and active living</t>
-  </si>
-  <si>
-    <t>Canadian Urological Association journal = Journal de l'Association des urologues</t>
-  </si>
-  <si>
-    <t>Annals of clinical and translational neurology</t>
-  </si>
-  <si>
-    <t>Clinical physiology and functional imaging</t>
-  </si>
-  <si>
-    <t>Journal of pain research</t>
-  </si>
-  <si>
-    <t>Cellular oncology (Dordrecht, Netherlands)</t>
-  </si>
-  <si>
-    <t>BMJ (Clinical research ed.)</t>
-  </si>
-  <si>
-    <t>International journal of urology : official journal of the Japanese Urological</t>
-  </si>
-  <si>
-    <t>Aesthetic surgery journal</t>
-  </si>
-  <si>
-    <t>Radiographics : a review publication of the Radiological Society of North</t>
-  </si>
-  <si>
-    <t>NMR in biomedicine</t>
-  </si>
-  <si>
-    <t>Zhonghua jie he he hu xi za zhi = Zhonghua jiehe he huxi zazhi = Chinese journal</t>
-  </si>
-  <si>
-    <t>Urologic oncology</t>
-  </si>
-  <si>
-    <t>Archives of gynecology and obstetrics</t>
-  </si>
-  <si>
-    <t>Journal of the anus, rectum and colon</t>
-  </si>
-  <si>
-    <t>Cartilage</t>
-  </si>
-  <si>
-    <t>Frontiers in public health</t>
-  </si>
-  <si>
-    <t>JACC. Cardiovascular imaging</t>
-  </si>
-  <si>
-    <t>European journal of ophthalmology</t>
-  </si>
-  <si>
-    <t>Journal of cardiovascular pharmacology</t>
-  </si>
-  <si>
-    <t>Nuklearmedizin. Nuclear medicine</t>
-  </si>
-  <si>
-    <t>Journal of dental research</t>
-  </si>
-  <si>
-    <t>Chinese medical journal</t>
-  </si>
-  <si>
-    <t>Journal of gastroenterology and hepatology</t>
-  </si>
-  <si>
-    <t>Current opinion in cardiology</t>
-  </si>
-  <si>
-    <t>Photoacoustics</t>
-  </si>
-  <si>
-    <t>Biological psychiatry</t>
-  </si>
-  <si>
-    <t>Frontiers in surgery</t>
-  </si>
-  <si>
-    <t>Legal medicine (Tokyo, Japan)</t>
-  </si>
-  <si>
-    <t>Digestive diseases and sciences</t>
-  </si>
-  <si>
-    <t>JAMA oncology</t>
-  </si>
-  <si>
-    <t>Frontiers in cardiovascular medicine</t>
+    <t>Thorax</t>
+  </si>
+  <si>
+    <t>Journal of neurosurgery. Spine</t>
+  </si>
+  <si>
+    <t>Obesity surgery</t>
+  </si>
+  <si>
+    <t>Adipocyte</t>
+  </si>
+  <si>
+    <t>Biophotonics discovery</t>
+  </si>
+  <si>
+    <t>Frontiers in neuroinformatics</t>
+  </si>
+  <si>
+    <t>Osteoporosis international : a journal established as result of cooperation</t>
+  </si>
+  <si>
+    <t>Emergency radiology</t>
+  </si>
+  <si>
+    <t>European journal of medicinal chemistry</t>
+  </si>
+  <si>
+    <t>BJU international</t>
+  </si>
+  <si>
+    <t>The Journal of international medical research</t>
+  </si>
+  <si>
+    <t>Biomolecules &amp; biomedicine</t>
+  </si>
+  <si>
+    <t>Journal of stomatology, oral and maxillofacial surgery</t>
+  </si>
+  <si>
+    <t>Cancer control : journal of the Moffitt Cancer Center</t>
+  </si>
+  <si>
+    <t>Journal of medical ultrasound</t>
+  </si>
+  <si>
+    <t>Frontiers in toxicology</t>
+  </si>
+  <si>
+    <t>The Journal of laryngology and otology</t>
+  </si>
+  <si>
+    <t>Critical reviews in oncology/hematology</t>
+  </si>
+  <si>
+    <t>Frontiers in big data</t>
+  </si>
+  <si>
+    <t>Frontiers in psychiatry</t>
+  </si>
+  <si>
+    <t>Obesity (Silver Spring, Md.)</t>
+  </si>
+  <si>
+    <t>Critical care (London, England)</t>
+  </si>
+  <si>
+    <t>Journal of cardiovascular magnetic resonance : official journal of the Society</t>
+  </si>
+  <si>
+    <t>Cell reports. Medicine</t>
+  </si>
+  <si>
+    <t>Journal of gastrointestinal oncology</t>
+  </si>
+  <si>
+    <t>Cardiovascular diagnosis and therapy</t>
+  </si>
+  <si>
+    <t>Cancer innovation</t>
+  </si>
+  <si>
+    <t>Journal of Parkinson's disease</t>
+  </si>
+  <si>
+    <t>Investigative radiology</t>
+  </si>
+  <si>
+    <t>Ophthalmology science</t>
+  </si>
+  <si>
+    <t>Liver transplantation : official publication of the American Association for the</t>
+  </si>
+  <si>
+    <t>International orthopaedics</t>
+  </si>
+  <si>
+    <t>Journal of neuroimaging : official journal of the American Society of</t>
+  </si>
+  <si>
+    <t>Therapeutic advances in medical oncology</t>
+  </si>
+  <si>
+    <t>BMC pulmonary medicine</t>
+  </si>
+  <si>
+    <t>American journal of Alzheimer's disease and other dementias</t>
+  </si>
+  <si>
+    <t>Acta oncologica (Stockholm, Sweden)</t>
+  </si>
+  <si>
+    <t>Thoracic cancer</t>
+  </si>
+  <si>
+    <t>Current radiopharmaceuticals</t>
+  </si>
+  <si>
+    <t>Brain &amp; spine</t>
+  </si>
+  <si>
+    <t>British journal of haematology</t>
+  </si>
+  <si>
+    <t>Rhinology</t>
+  </si>
+  <si>
+    <t>MethodsX</t>
+  </si>
+  <si>
+    <t>Internal medicine (Tokyo, Japan)</t>
+  </si>
+  <si>
+    <t>The Journal of hand surgery, European volume</t>
+  </si>
+  <si>
+    <t>Biochimica et biophysica acta. Molecular basis of disease</t>
+  </si>
+  <si>
+    <t>Annali italiani di chirurgia</t>
+  </si>
+  <si>
+    <t>Progress in biomedical engineering (Bristol, England)</t>
+  </si>
+  <si>
+    <t>Hepatology (Baltimore, Md.)</t>
+  </si>
+  <si>
+    <t>Current medical science</t>
+  </si>
+  <si>
+    <t>Journal of nuclear medicine : official publication, Society of Nuclear Medicine</t>
+  </si>
+  <si>
+    <t>Parkinsonism &amp; related disorders</t>
+  </si>
+  <si>
+    <t>Investigative ophthalmology &amp; visual science</t>
   </si>
   <si>
     <t>Urolithiasis</t>
   </si>
   <si>
-    <t>The neurologist</t>
-  </si>
-  <si>
-    <t>Neurogastroenterology and motility</t>
-  </si>
-  <si>
-    <t>Asian journal of psychiatry</t>
-  </si>
-  <si>
-    <t>The Journal of biological chemistry</t>
-  </si>
-  <si>
-    <t>Nuclear medicine and molecular imaging</t>
-  </si>
-  <si>
-    <t>International forum of allergy &amp; rhinology</t>
-  </si>
-  <si>
-    <t>African journal of reproductive health</t>
-  </si>
-  <si>
-    <t>JMIR AI</t>
-  </si>
-  <si>
-    <t>The Lancet. Rheumatology</t>
-  </si>
-  <si>
-    <t>Clinical rheumatology</t>
-  </si>
-  <si>
-    <t>Brain research</t>
-  </si>
-  <si>
-    <t>Chinese neurosurgical journal</t>
-  </si>
-  <si>
-    <t>Zhonghua yi xue za zhi</t>
-  </si>
-  <si>
-    <t>American Society of Clinical Oncology educational book. American Society of</t>
-  </si>
-  <si>
-    <t>Zhonghua wei chang wai ke za zhi = Chinese journal of gastrointestinal surgery</t>
-  </si>
-  <si>
-    <t>BMC cardiovascular disorders</t>
-  </si>
-  <si>
-    <t>Journal of cardiovascular computed tomography</t>
-  </si>
-  <si>
-    <t>Journal of medical signals and sensors</t>
-  </si>
-  <si>
-    <t>Medical oncology (Northwood, London, England)</t>
-  </si>
-  <si>
-    <t>Veterinary sciences</t>
-  </si>
-  <si>
-    <t>BJS open</t>
-  </si>
-  <si>
-    <t>Breast cancer research and treatment</t>
-  </si>
-  <si>
-    <t>Translational andrology and urology</t>
-  </si>
-  <si>
-    <t>Frontiers in genetics</t>
-  </si>
-  <si>
-    <t>Clinical and translational radiation oncology</t>
-  </si>
-  <si>
-    <t>Pancreatology : official journal of the International Association of</t>
-  </si>
-  <si>
-    <t>EJNMMI reports</t>
-  </si>
-  <si>
-    <t>Molecular biomedicine</t>
-  </si>
-  <si>
-    <t>Science progress</t>
-  </si>
-  <si>
-    <t>Gynecologic and obstetric investigation</t>
-  </si>
-  <si>
-    <t>Techniques in coloproctology</t>
-  </si>
-  <si>
-    <t>Medical ultrasonography</t>
-  </si>
-  <si>
-    <t>International journal of chronic obstructive pulmonary disease</t>
-  </si>
-  <si>
-    <t>Cardiology journal</t>
-  </si>
-  <si>
-    <t>BMC surgery</t>
-  </si>
-  <si>
-    <t>Healthcare (Basel, Switzerland)</t>
-  </si>
-  <si>
-    <t>JAMA cardiology</t>
-  </si>
-  <si>
-    <t>Clinical &amp; experimental metastasis</t>
-  </si>
-  <si>
-    <t>International journal of women's health</t>
-  </si>
-  <si>
-    <t>Circulation research</t>
-  </si>
-  <si>
-    <t>Haematologica</t>
-  </si>
-  <si>
-    <t>The Lancet regional health. Western Pacific</t>
-  </si>
-  <si>
-    <t>Gastroenterology report</t>
-  </si>
-  <si>
-    <t>Journal of clinical neuroscience : official journal of the Neurosurgical Society</t>
-  </si>
-  <si>
-    <t>Urologie (Heidelberg, Germany)</t>
-  </si>
-  <si>
-    <t>Adipocyte</t>
-  </si>
-  <si>
-    <t>Obesity surgery</t>
-  </si>
-  <si>
-    <t>Journal of neurosurgery. Spine</t>
-  </si>
-  <si>
-    <t>Thorax</t>
-  </si>
-  <si>
-    <t>European urology</t>
-  </si>
-  <si>
-    <t>Brain topography</t>
-  </si>
-  <si>
-    <t>Advanced biology</t>
-  </si>
-  <si>
-    <t>Oncology letters</t>
-  </si>
-  <si>
-    <t>Journal of medical imaging and radiation sciences</t>
-  </si>
-  <si>
-    <t>Biomedical reports</t>
-  </si>
-  <si>
-    <t>Research (Washington, D.C.)</t>
-  </si>
-  <si>
-    <t>Journal of oral pathology &amp; medicine : official publication of the International</t>
-  </si>
-  <si>
-    <t>Naunyn-Schmiedeberg's archives of pharmacology</t>
-  </si>
-  <si>
-    <t>Cerebral cortex (New York, N.Y. : 1991)</t>
-  </si>
-  <si>
-    <t>Visceral medicine</t>
-  </si>
-  <si>
-    <t>Frontiers in pediatrics</t>
-  </si>
-  <si>
-    <t>Frontiers in dental medicine</t>
-  </si>
-  <si>
-    <t>BMJ open respiratory research</t>
-  </si>
-  <si>
-    <t>Biophotonics discovery</t>
+    <t>Zhonghua kou qiang yi xue za zhi = Zhonghua kouqiang yixue zazhi = Chinese</t>
+  </si>
+  <si>
+    <t>Translational vision science &amp; technology</t>
+  </si>
+  <si>
+    <t>Science advances</t>
+  </si>
+  <si>
+    <t>Calcified tissue international</t>
+  </si>
+  <si>
+    <t>Oral oncology</t>
+  </si>
+  <si>
+    <t>Asia-Pacific journal of clinical oncology</t>
+  </si>
+  <si>
+    <t>BMC neuroscience</t>
+  </si>
+  <si>
+    <t>Frontiers in bioscience (Landmark edition)</t>
+  </si>
+  <si>
+    <t>International journal of cancer</t>
+  </si>
+  <si>
+    <t>Neurospine</t>
+  </si>
+  <si>
+    <t>Best practice &amp; research. Clinical gastroenterology</t>
+  </si>
+  <si>
+    <t>F1000Research</t>
+  </si>
+  <si>
+    <t>Small methods</t>
+  </si>
+  <si>
+    <t>Reproductive biomedicine online</t>
+  </si>
+  <si>
+    <t>Brain connectivity</t>
+  </si>
+  <si>
+    <t>Current cardiology reports</t>
+  </si>
+  <si>
+    <t>Amyloid : the international journal of experimental and clinical investigation :</t>
+  </si>
+  <si>
+    <t>BMC immunology</t>
+  </si>
+  <si>
+    <t>Radiologia</t>
   </si>
   <si>
     <t>Data in brief</t>
   </si>
   <si>
-    <t>Biomolecules &amp; biomedicine</t>
-  </si>
-  <si>
-    <t>Journal of stomatology, oral and maxillofacial surgery</t>
-  </si>
-  <si>
-    <t>Veterinary and comparative oncology</t>
-  </si>
-  <si>
-    <t>Statistics in medicine</t>
-  </si>
-  <si>
-    <t>Philosophical transactions. Series A, Mathematical, physical, and engineering</t>
-  </si>
-  <si>
-    <t>European journal of pediatrics</t>
-  </si>
-  <si>
-    <t>Frontiers in pharmacology</t>
-  </si>
-  <si>
-    <t>Global spine journal</t>
-  </si>
-  <si>
-    <t>Acta cardiologica</t>
-  </si>
-  <si>
-    <t>World journal of hepatology</t>
-  </si>
-  <si>
-    <t>Research in diagnostic and interventional imaging</t>
-  </si>
-  <si>
-    <t>Parkinsonism &amp; related disorders</t>
-  </si>
-  <si>
-    <t>Journal of nuclear medicine : official publication, Society of Nuclear Medicine</t>
-  </si>
-  <si>
-    <t>Current medical science</t>
-  </si>
-  <si>
-    <t>Hepatology (Baltimore, Md.)</t>
-  </si>
-  <si>
-    <t>Oral oncology</t>
-  </si>
-  <si>
-    <t>Annali italiani di chirurgia</t>
-  </si>
-  <si>
-    <t>Journal of medical ultrasound</t>
-  </si>
-  <si>
-    <t>Cancer control : journal of the Moffitt Cancer Center</t>
-  </si>
-  <si>
-    <t>Journal of global antimicrobial resistance</t>
-  </si>
-  <si>
-    <t>The Journal of craniofacial surgery</t>
-  </si>
-  <si>
-    <t>Canadian Association of Radiologists journal = Journal l'Association canadienne</t>
-  </si>
-  <si>
-    <t>European journal of medicinal chemistry</t>
-  </si>
-  <si>
-    <t>Journal of Parkinson's disease</t>
-  </si>
-  <si>
-    <t>Thoracic cancer</t>
-  </si>
-  <si>
-    <t>Cardiovascular diagnosis and therapy</t>
-  </si>
-  <si>
-    <t>Journal of gastrointestinal oncology</t>
-  </si>
-  <si>
-    <t>Cell reports. Medicine</t>
-  </si>
-  <si>
-    <t>Journal of cardiovascular magnetic resonance : official journal of the Society</t>
-  </si>
-  <si>
-    <t>The Journal of international medical research</t>
-  </si>
-  <si>
-    <t>BJU international</t>
-  </si>
-  <si>
-    <t>Emergency radiology</t>
-  </si>
-  <si>
-    <t>Hepatology research : the official journal of the Japan Society of Hepatology</t>
-  </si>
-  <si>
-    <t>Osteoporosis international : a journal established as result of cooperation</t>
-  </si>
-  <si>
-    <t>The Journal of laryngology and otology</t>
-  </si>
-  <si>
-    <t>Journal of orthopaedic translation</t>
-  </si>
-  <si>
-    <t>Ginekologia polska</t>
-  </si>
-  <si>
-    <t>Seminars in cancer biology</t>
-  </si>
-  <si>
-    <t>Frontiers in bioscience (Landmark edition)</t>
-  </si>
-  <si>
-    <t>BMC neuroscience</t>
-  </si>
-  <si>
-    <t>Asia-Pacific journal of clinical oncology</t>
-  </si>
-  <si>
-    <t>Investigative radiology</t>
-  </si>
-  <si>
-    <t>Ophthalmology science</t>
-  </si>
-  <si>
-    <t>Liver transplantation : official publication of the American Association for the</t>
-  </si>
-  <si>
-    <t>International orthopaedics</t>
-  </si>
-  <si>
-    <t>Cancer radiotherapie : journal de la Societe francaise de radiotherapie</t>
-  </si>
-  <si>
-    <t>The Journal of infection</t>
-  </si>
-  <si>
-    <t>Critical care (London, England)</t>
-  </si>
-  <si>
-    <t>Obesity (Silver Spring, Md.)</t>
-  </si>
-  <si>
-    <t>Frontiers in psychiatry</t>
-  </si>
-  <si>
-    <t>Frontiers in big data</t>
-  </si>
-  <si>
-    <t>Critical reviews in oncology/hematology</t>
-  </si>
-  <si>
-    <t>Cancer prevention research (Philadelphia, Pa.)</t>
-  </si>
-  <si>
-    <t>Cancer cell</t>
-  </si>
-  <si>
-    <t>Rheumatology (Oxford, England)</t>
-  </si>
-  <si>
-    <t>Frontiers in veterinary science</t>
-  </si>
-  <si>
-    <t>Cancer innovation</t>
-  </si>
-  <si>
-    <t>Acta oncologica (Stockholm, Sweden)</t>
-  </si>
-  <si>
-    <t>American journal of Alzheimer's disease and other dementias</t>
-  </si>
-  <si>
-    <t>BMC pulmonary medicine</t>
-  </si>
-  <si>
-    <t>Therapeutic advances in medical oncology</t>
-  </si>
-  <si>
-    <t>Journal of neuroimaging : official journal of the American Society of</t>
-  </si>
-  <si>
-    <t>Progress in biomedical engineering (Bristol, England)</t>
-  </si>
-  <si>
-    <t>Frontiers in toxicology</t>
-  </si>
-  <si>
-    <t>Radiologia</t>
+    <t>Journal of the National Cancer Center</t>
+  </si>
+  <si>
+    <t>Actas urologicas espanolas</t>
+  </si>
+  <si>
+    <t>Rheumatology advances in practice</t>
+  </si>
+  <si>
+    <t>Journal of medical physics</t>
   </si>
   <si>
     <t>JCO precision oncology</t>
   </si>
   <si>
-    <t>Rheumatology advances in practice</t>
-  </si>
-  <si>
-    <t>Actas urologicas espanolas</t>
-  </si>
-  <si>
-    <t>Journal of the National Cancer Center</t>
-  </si>
-  <si>
-    <t>Translational vision science &amp; technology</t>
-  </si>
-  <si>
-    <t>Zhonghua kou qiang yi xue za zhi = Zhonghua kouqiang yixue zazhi = Chinese</t>
-  </si>
-  <si>
-    <t>Investigative ophthalmology &amp; visual science</t>
-  </si>
-  <si>
-    <t>IEEE transactions on neural networks and learning systems</t>
-  </si>
-  <si>
-    <t>The Journal of urology</t>
-  </si>
-  <si>
-    <t>Anticancer research</t>
-  </si>
-  <si>
-    <t>BJR artificial intelligence</t>
-  </si>
-  <si>
-    <t>Cancer discovery</t>
-  </si>
-  <si>
-    <t>Proceedings of SPIE--the International Society for Optical Engineering</t>
-  </si>
-  <si>
-    <t>Biochimica et biophysica acta. Reviews on cancer</t>
-  </si>
-  <si>
-    <t>Acta obstetricia et gynecologica Scandinavica</t>
-  </si>
-  <si>
-    <t>Frontiers in neuroinformatics</t>
-  </si>
-  <si>
-    <t>Calcified tissue international</t>
-  </si>
-  <si>
-    <t>Science advances</t>
-  </si>
-  <si>
-    <t>Journal of medical physics</t>
-  </si>
-  <si>
     <t>Journal of the Chinese Medical Association : JCMA</t>
   </si>
   <si>
-    <t>BMC immunology</t>
-  </si>
-  <si>
-    <t>Current cardiology reports</t>
-  </si>
-  <si>
-    <t>Amyloid : the international journal of experimental and clinical investigation :</t>
-  </si>
-  <si>
     <t>Journal of clinical sleep medicine : JCSM : official publication of the American</t>
-  </si>
-  <si>
-    <t>Brain connectivity</t>
-  </si>
-  <si>
-    <t>Reproductive biomedicine online</t>
-  </si>
-  <si>
-    <t>Small methods</t>
-  </si>
-  <si>
-    <t>F1000Research</t>
-  </si>
-  <si>
-    <t>Best practice &amp; research. Clinical gastroenterology</t>
-  </si>
-  <si>
-    <t>Neurospine</t>
-  </si>
-  <si>
-    <t>International journal of cancer</t>
-  </si>
-  <si>
-    <t>Biochimica et biophysica acta. Molecular basis of disease</t>
-  </si>
-  <si>
-    <t>The Journal of hand surgery, European volume</t>
-  </si>
-  <si>
-    <t>Internal medicine (Tokyo, Japan)</t>
-  </si>
-  <si>
-    <t>MethodsX</t>
-  </si>
-  <si>
-    <t>Rhinology</t>
-  </si>
-  <si>
-    <t>British journal of haematology</t>
-  </si>
-  <si>
-    <t>Brain &amp; spine</t>
-  </si>
-  <si>
-    <t>Current radiopharmaceuticals</t>
-  </si>
-  <si>
-    <t>Annals of surgery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1754,14 +1748,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1808,7 +1794,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1840,27 +1826,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1892,24 +1860,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2085,14 +2035,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B554"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="31.1640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2100,7 +2047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2108,7 +2055,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2116,7 +2063,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2124,7 +2071,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2132,7 +2079,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2140,7 +2087,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2148,7 +2095,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2103,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2164,7 +2111,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2172,7 +2119,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2180,7 +2127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2188,7 +2135,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2196,7 +2143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2204,7 +2151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2212,7 +2159,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2220,7 +2167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2228,7 +2175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2236,7 +2183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2244,7 +2191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2252,7 +2199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2260,7 +2207,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2268,7 +2215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2276,7 +2223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2284,7 +2231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2292,7 +2239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2300,7 +2247,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2308,7 +2255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2316,7 +2263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2324,7 +2271,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2332,7 +2279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2340,7 +2287,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2348,7 +2295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2356,7 +2303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2364,7 +2311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2372,7 +2319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2380,7 +2327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2388,7 +2335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2396,7 +2343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2404,7 +2351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2412,7 +2359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2420,7 +2367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2428,7 +2375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2436,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2444,7 +2391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2452,7 +2399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -2460,7 +2407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2468,7 +2415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -2476,7 +2423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -2484,7 +2431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2492,7 +2439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -2500,7 +2447,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2508,7 +2455,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -2516,7 +2463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -2524,7 +2471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2532,7 +2479,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -2540,7 +2487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -2548,7 +2495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -2556,7 +2503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -2564,7 +2511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -2572,7 +2519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2580,7 +2527,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -2588,7 +2535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -2596,7 +2543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -2604,7 +2551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -2612,7 +2559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -2620,7 +2567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -2628,7 +2575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -2636,7 +2583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -2644,7 +2591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -2652,7 +2599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -2660,7 +2607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -2668,7 +2615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -2676,7 +2623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -2684,7 +2631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -2692,7 +2639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -2700,7 +2647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>77</v>
       </c>
@@ -2708,7 +2655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2716,7 +2663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -2724,7 +2671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2732,7 +2679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -2740,7 +2687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -2748,7 +2695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2756,7 +2703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -2764,7 +2711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -2772,7 +2719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -2780,7 +2727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -2788,7 +2735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -2796,7 +2743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -2804,7 +2751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -2812,7 +2759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -2820,7 +2767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -2828,7 +2775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -2836,7 +2783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -2844,7 +2791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -2852,7 +2799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -2860,7 +2807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -2868,7 +2815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>98</v>
       </c>
@@ -2876,7 +2823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -2884,7 +2831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -2892,7 +2839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -2900,7 +2847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -2908,7 +2855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -2916,7 +2863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -2924,7 +2871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -2932,7 +2879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -2940,7 +2887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -2948,7 +2895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -2956,7 +2903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -2964,7 +2911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -2972,7 +2919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -2980,7 +2927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -2988,7 +2935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -2996,7 +2943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -3004,7 +2951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3012,7 +2959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -3020,7 +2967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -3028,7 +2975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -3036,7 +2983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -3044,7 +2991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -3052,7 +2999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -3060,7 +3007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -3068,7 +3015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -3076,7 +3023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -3084,7 +3031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -3092,7 +3039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -3100,7 +3047,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>127</v>
       </c>
@@ -3108,7 +3055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>128</v>
       </c>
@@ -3116,7 +3063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>129</v>
       </c>
@@ -3124,7 +3071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>130</v>
       </c>
@@ -3132,7 +3079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>131</v>
       </c>
@@ -3140,7 +3087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -3148,7 +3095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>133</v>
       </c>
@@ -3156,7 +3103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>134</v>
       </c>
@@ -3164,7 +3111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>135</v>
       </c>
@@ -3172,7 +3119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>136</v>
       </c>
@@ -3180,7 +3127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>137</v>
       </c>
@@ -3188,7 +3135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>138</v>
       </c>
@@ -3196,7 +3143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -3204,7 +3151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -3212,7 +3159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>141</v>
       </c>
@@ -3220,7 +3167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>142</v>
       </c>
@@ -3228,7 +3175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -3236,7 +3183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>144</v>
       </c>
@@ -3244,7 +3191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>145</v>
       </c>
@@ -3252,7 +3199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>146</v>
       </c>
@@ -3260,7 +3207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -3268,7 +3215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>148</v>
       </c>
@@ -3276,7 +3223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>149</v>
       </c>
@@ -3284,7 +3231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -3292,7 +3239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>151</v>
       </c>
@@ -3300,7 +3247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>152</v>
       </c>
@@ -3308,7 +3255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>153</v>
       </c>
@@ -3316,7 +3263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -3324,7 +3271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>155</v>
       </c>
@@ -3332,7 +3279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>156</v>
       </c>
@@ -3340,7 +3287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>157</v>
       </c>
@@ -3348,7 +3295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>158</v>
       </c>
@@ -3356,7 +3303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>159</v>
       </c>
@@ -3364,7 +3311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -3372,7 +3319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>161</v>
       </c>
@@ -3380,7 +3327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>162</v>
       </c>
@@ -3388,7 +3335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>163</v>
       </c>
@@ -3396,7 +3343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>164</v>
       </c>
@@ -3404,7 +3351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>165</v>
       </c>
@@ -3412,7 +3359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>166</v>
       </c>
@@ -3420,7 +3367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>167</v>
       </c>
@@ -3428,7 +3375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2">
       <c r="A168" t="s">
         <v>168</v>
       </c>
@@ -3436,7 +3383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2">
       <c r="A169" t="s">
         <v>169</v>
       </c>
@@ -3444,7 +3391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2">
       <c r="A170" t="s">
         <v>170</v>
       </c>
@@ -3452,7 +3399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2">
       <c r="A171" t="s">
         <v>171</v>
       </c>
@@ -3460,7 +3407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2">
       <c r="A172" t="s">
         <v>172</v>
       </c>
@@ -3468,7 +3415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2">
       <c r="A173" t="s">
         <v>173</v>
       </c>
@@ -3476,7 +3423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
         <v>174</v>
       </c>
@@ -3484,7 +3431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2">
       <c r="A175" t="s">
         <v>175</v>
       </c>
@@ -3492,7 +3439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
         <v>176</v>
       </c>
@@ -3500,7 +3447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>177</v>
       </c>
@@ -3508,7 +3455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>178</v>
       </c>
@@ -3516,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>179</v>
       </c>
@@ -3524,7 +3471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>180</v>
       </c>
@@ -3532,7 +3479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>181</v>
       </c>
@@ -3540,7 +3487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>182</v>
       </c>
@@ -3548,7 +3495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>183</v>
       </c>
@@ -3556,7 +3503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>184</v>
       </c>
@@ -3564,7 +3511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>185</v>
       </c>
@@ -3572,7 +3519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>186</v>
       </c>
@@ -3580,7 +3527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>187</v>
       </c>
@@ -3588,7 +3535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>188</v>
       </c>
@@ -3596,7 +3543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>189</v>
       </c>
@@ -3604,7 +3551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>190</v>
       </c>
@@ -3612,7 +3559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>191</v>
       </c>
@@ -3620,7 +3567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>192</v>
       </c>
@@ -3628,7 +3575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2">
       <c r="A193" t="s">
         <v>193</v>
       </c>
@@ -3636,7 +3583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2">
       <c r="A194" t="s">
         <v>194</v>
       </c>
@@ -3644,7 +3591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2">
       <c r="A195" t="s">
         <v>195</v>
       </c>
@@ -3652,7 +3599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2">
       <c r="A196" t="s">
         <v>196</v>
       </c>
@@ -3660,7 +3607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2">
       <c r="A197" t="s">
         <v>197</v>
       </c>
@@ -3668,7 +3615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2">
       <c r="A198" t="s">
         <v>198</v>
       </c>
@@ -3676,7 +3623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -3684,7 +3631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2">
       <c r="A200" t="s">
         <v>200</v>
       </c>
@@ -3692,7 +3639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2">
       <c r="A201" t="s">
         <v>201</v>
       </c>
@@ -3700,7 +3647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2">
       <c r="A202" t="s">
         <v>202</v>
       </c>
@@ -3708,7 +3655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2">
       <c r="A203" t="s">
         <v>203</v>
       </c>
@@ -3716,7 +3663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2">
       <c r="A204" t="s">
         <v>204</v>
       </c>
@@ -3724,7 +3671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2">
       <c r="A205" t="s">
         <v>205</v>
       </c>
@@ -3732,7 +3679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2">
       <c r="A206" t="s">
         <v>206</v>
       </c>
@@ -3740,7 +3687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2">
       <c r="A207" t="s">
         <v>207</v>
       </c>
@@ -3748,7 +3695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2">
       <c r="A208" t="s">
         <v>208</v>
       </c>
@@ -3756,7 +3703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2">
       <c r="A209" t="s">
         <v>209</v>
       </c>
@@ -3764,7 +3711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2">
       <c r="A210" t="s">
         <v>210</v>
       </c>
@@ -3772,7 +3719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2">
       <c r="A211" t="s">
         <v>211</v>
       </c>
@@ -3780,7 +3727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2">
       <c r="A212" t="s">
         <v>212</v>
       </c>
@@ -3788,7 +3735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2">
       <c r="A213" t="s">
         <v>213</v>
       </c>
@@ -3796,7 +3743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2">
       <c r="A214" t="s">
         <v>214</v>
       </c>
@@ -3804,7 +3751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2">
       <c r="A215" t="s">
         <v>215</v>
       </c>
@@ -3812,7 +3759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2">
       <c r="A216" t="s">
         <v>216</v>
       </c>
@@ -3820,7 +3767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2">
       <c r="A217" t="s">
         <v>217</v>
       </c>
@@ -3828,7 +3775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2">
       <c r="A218" t="s">
         <v>218</v>
       </c>
@@ -3836,7 +3783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2">
       <c r="A219" t="s">
         <v>219</v>
       </c>
@@ -3844,7 +3791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2">
       <c r="A220" t="s">
         <v>220</v>
       </c>
@@ -3852,7 +3799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2">
       <c r="A221" t="s">
         <v>221</v>
       </c>
@@ -3860,7 +3807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2">
       <c r="A222" t="s">
         <v>222</v>
       </c>
@@ -3868,7 +3815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2">
       <c r="A223" t="s">
         <v>223</v>
       </c>
@@ -3876,7 +3823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2">
       <c r="A224" t="s">
         <v>224</v>
       </c>
@@ -3884,7 +3831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2">
       <c r="A225" t="s">
         <v>225</v>
       </c>
@@ -3892,7 +3839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2">
       <c r="A226" t="s">
         <v>226</v>
       </c>
@@ -3900,7 +3847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2">
       <c r="A227" t="s">
         <v>227</v>
       </c>
@@ -3908,7 +3855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2">
       <c r="A228" t="s">
         <v>228</v>
       </c>
@@ -3916,7 +3863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2">
       <c r="A229" t="s">
         <v>229</v>
       </c>
@@ -3924,7 +3871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2">
       <c r="A230" t="s">
         <v>230</v>
       </c>
@@ -3932,7 +3879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2">
       <c r="A231" t="s">
         <v>231</v>
       </c>
@@ -3940,7 +3887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2">
       <c r="A232" t="s">
         <v>232</v>
       </c>
@@ -3948,7 +3895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2">
       <c r="A233" t="s">
         <v>233</v>
       </c>
@@ -3956,7 +3903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2">
       <c r="A234" t="s">
         <v>234</v>
       </c>
@@ -3964,7 +3911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2">
       <c r="A235" t="s">
         <v>235</v>
       </c>
@@ -3972,7 +3919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2">
       <c r="A236" t="s">
         <v>236</v>
       </c>
@@ -3980,7 +3927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2">
       <c r="A237" t="s">
         <v>237</v>
       </c>
@@ -3988,7 +3935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2">
       <c r="A238" t="s">
         <v>238</v>
       </c>
@@ -3996,7 +3943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2">
       <c r="A239" t="s">
         <v>239</v>
       </c>
@@ -4004,7 +3951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2">
       <c r="A240" t="s">
         <v>240</v>
       </c>
@@ -4012,7 +3959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2">
       <c r="A241" t="s">
         <v>241</v>
       </c>
@@ -4020,7 +3967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2">
       <c r="A242" t="s">
         <v>242</v>
       </c>
@@ -4028,7 +3975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2">
       <c r="A243" t="s">
         <v>243</v>
       </c>
@@ -4036,7 +3983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2">
       <c r="A244" t="s">
         <v>244</v>
       </c>
@@ -4044,7 +3991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2">
       <c r="A245" t="s">
         <v>245</v>
       </c>
@@ -4052,7 +3999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2">
       <c r="A246" t="s">
         <v>246</v>
       </c>
@@ -4060,7 +4007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2">
       <c r="A247" t="s">
         <v>247</v>
       </c>
@@ -4068,7 +4015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2">
       <c r="A248" t="s">
         <v>248</v>
       </c>
@@ -4076,7 +4023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2">
       <c r="A249" t="s">
         <v>249</v>
       </c>
@@ -4084,7 +4031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2">
       <c r="A250" t="s">
         <v>250</v>
       </c>
@@ -4092,7 +4039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2">
       <c r="A251" t="s">
         <v>251</v>
       </c>
@@ -4100,7 +4047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:2">
       <c r="A252" t="s">
         <v>252</v>
       </c>
@@ -4108,7 +4055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:2">
       <c r="A253" t="s">
         <v>253</v>
       </c>
@@ -4116,7 +4063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:2">
       <c r="A254" t="s">
         <v>254</v>
       </c>
@@ -4124,7 +4071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:2">
       <c r="A255" t="s">
         <v>255</v>
       </c>
@@ -4132,7 +4079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:2">
       <c r="A256" t="s">
         <v>256</v>
       </c>
@@ -4140,7 +4087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:2">
       <c r="A257" t="s">
         <v>257</v>
       </c>
@@ -4148,7 +4095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:2">
       <c r="A258" t="s">
         <v>258</v>
       </c>
@@ -4156,7 +4103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:2">
       <c r="A259" t="s">
         <v>259</v>
       </c>
@@ -4164,7 +4111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:2">
       <c r="A260" t="s">
         <v>260</v>
       </c>
@@ -4172,7 +4119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:2">
       <c r="A261" t="s">
         <v>261</v>
       </c>
@@ -4180,7 +4127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:2">
       <c r="A262" t="s">
         <v>262</v>
       </c>
@@ -4188,7 +4135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:2">
       <c r="A263" t="s">
         <v>263</v>
       </c>
@@ -4196,7 +4143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:2">
       <c r="A264" t="s">
         <v>264</v>
       </c>
@@ -4204,7 +4151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:2">
       <c r="A265" t="s">
         <v>265</v>
       </c>
@@ -4212,7 +4159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:2">
       <c r="A266" t="s">
         <v>266</v>
       </c>
@@ -4220,7 +4167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:2">
       <c r="A267" t="s">
         <v>267</v>
       </c>
@@ -4228,7 +4175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:2">
       <c r="A268" t="s">
         <v>268</v>
       </c>
@@ -4236,7 +4183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:2">
       <c r="A269" t="s">
         <v>269</v>
       </c>
@@ -4244,7 +4191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:2">
       <c r="A270" t="s">
         <v>270</v>
       </c>
@@ -4252,7 +4199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:2">
       <c r="A271" t="s">
         <v>271</v>
       </c>
@@ -4260,7 +4207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:2">
       <c r="A272" t="s">
         <v>272</v>
       </c>
@@ -4268,7 +4215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:2">
       <c r="A273" t="s">
         <v>273</v>
       </c>
@@ -4276,7 +4223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:2">
       <c r="A274" t="s">
         <v>274</v>
       </c>
@@ -4284,7 +4231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:2">
       <c r="A275" t="s">
         <v>275</v>
       </c>
@@ -4292,7 +4239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:2">
       <c r="A276" t="s">
         <v>276</v>
       </c>
@@ -4300,7 +4247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:2">
       <c r="A277" t="s">
         <v>277</v>
       </c>
@@ -4308,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:2">
       <c r="A278" t="s">
         <v>278</v>
       </c>
@@ -4316,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:2">
       <c r="A279" t="s">
         <v>279</v>
       </c>
@@ -4324,7 +4271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:2">
       <c r="A280" t="s">
         <v>280</v>
       </c>
@@ -4332,7 +4279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:2">
       <c r="A281" t="s">
         <v>281</v>
       </c>
@@ -4340,7 +4287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:2">
       <c r="A282" t="s">
         <v>282</v>
       </c>
@@ -4348,7 +4295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:2">
       <c r="A283" t="s">
         <v>283</v>
       </c>
@@ -4356,7 +4303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:2">
       <c r="A284" t="s">
         <v>284</v>
       </c>
@@ -4364,7 +4311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:2">
       <c r="A285" t="s">
         <v>285</v>
       </c>
@@ -4372,7 +4319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:2">
       <c r="A286" t="s">
         <v>286</v>
       </c>
@@ -4380,7 +4327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:2">
       <c r="A287" t="s">
         <v>287</v>
       </c>
@@ -4388,7 +4335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:2">
       <c r="A288" t="s">
         <v>288</v>
       </c>
@@ -4396,7 +4343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:2">
       <c r="A289" t="s">
         <v>289</v>
       </c>
@@ -4404,7 +4351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:2">
       <c r="A290" t="s">
         <v>290</v>
       </c>
@@ -4412,7 +4359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:2">
       <c r="A291" t="s">
         <v>291</v>
       </c>
@@ -4420,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:2">
       <c r="A292" t="s">
         <v>292</v>
       </c>
@@ -4428,7 +4375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:2">
       <c r="A293" t="s">
         <v>293</v>
       </c>
@@ -4436,7 +4383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:2">
       <c r="A294" t="s">
         <v>294</v>
       </c>
@@ -4444,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:2">
       <c r="A295" t="s">
         <v>295</v>
       </c>
@@ -4452,7 +4399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:2">
       <c r="A296" t="s">
         <v>296</v>
       </c>
@@ -4460,7 +4407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:2">
       <c r="A297" t="s">
         <v>297</v>
       </c>
@@ -4468,7 +4415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:2">
       <c r="A298" t="s">
         <v>298</v>
       </c>
@@ -4476,7 +4423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:2">
       <c r="A299" t="s">
         <v>299</v>
       </c>
@@ -4484,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:2">
       <c r="A300" t="s">
         <v>300</v>
       </c>
@@ -4492,7 +4439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:2">
       <c r="A301" t="s">
         <v>301</v>
       </c>
@@ -4500,7 +4447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:2">
       <c r="A302" t="s">
         <v>302</v>
       </c>
@@ -4508,7 +4455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:2">
       <c r="A303" t="s">
         <v>303</v>
       </c>
@@ -4516,7 +4463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:2">
       <c r="A304" t="s">
         <v>304</v>
       </c>
@@ -4524,7 +4471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:2">
       <c r="A305" t="s">
         <v>305</v>
       </c>
@@ -4532,7 +4479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:2">
       <c r="A306" t="s">
         <v>306</v>
       </c>
@@ -4540,7 +4487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:2">
       <c r="A307" t="s">
         <v>307</v>
       </c>
@@ -4548,7 +4495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:2">
       <c r="A308" t="s">
         <v>308</v>
       </c>
@@ -4556,7 +4503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:2">
       <c r="A309" t="s">
         <v>309</v>
       </c>
@@ -4564,7 +4511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:2">
       <c r="A310" t="s">
         <v>310</v>
       </c>
@@ -4572,7 +4519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:2">
       <c r="A311" t="s">
         <v>311</v>
       </c>
@@ -4580,7 +4527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:2">
       <c r="A312" t="s">
         <v>312</v>
       </c>
@@ -4588,7 +4535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:2">
       <c r="A313" t="s">
         <v>313</v>
       </c>
@@ -4596,7 +4543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:2">
       <c r="A314" t="s">
         <v>314</v>
       </c>
@@ -4604,7 +4551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:2">
       <c r="A315" t="s">
         <v>315</v>
       </c>
@@ -4612,7 +4559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:2">
       <c r="A316" t="s">
         <v>316</v>
       </c>
@@ -4620,7 +4567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:2">
       <c r="A317" t="s">
         <v>317</v>
       </c>
@@ -4628,7 +4575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:2">
       <c r="A318" t="s">
         <v>318</v>
       </c>
@@ -4636,7 +4583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:2">
       <c r="A319" t="s">
         <v>319</v>
       </c>
@@ -4644,7 +4591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:2">
       <c r="A320" t="s">
         <v>320</v>
       </c>
@@ -4652,7 +4599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:2">
       <c r="A321" t="s">
         <v>321</v>
       </c>
@@ -4660,7 +4607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:2">
       <c r="A322" t="s">
         <v>322</v>
       </c>
@@ -4668,7 +4615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:2">
       <c r="A323" t="s">
         <v>323</v>
       </c>
@@ -4676,7 +4623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:2">
       <c r="A324" t="s">
         <v>324</v>
       </c>
@@ -4684,7 +4631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:2">
       <c r="A325" t="s">
         <v>325</v>
       </c>
@@ -4692,7 +4639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:2">
       <c r="A326" t="s">
         <v>326</v>
       </c>
@@ -4700,7 +4647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:2">
       <c r="A327" t="s">
         <v>327</v>
       </c>
@@ -4708,7 +4655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:2">
       <c r="A328" t="s">
         <v>328</v>
       </c>
@@ -4716,7 +4663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:2">
       <c r="A329" t="s">
         <v>329</v>
       </c>
@@ -4724,7 +4671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:2">
       <c r="A330" t="s">
         <v>330</v>
       </c>
@@ -4732,7 +4679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:2">
       <c r="A331" t="s">
         <v>331</v>
       </c>
@@ -4740,7 +4687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:2">
       <c r="A332" t="s">
         <v>332</v>
       </c>
@@ -4748,7 +4695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:2">
       <c r="A333" t="s">
         <v>333</v>
       </c>
@@ -4756,7 +4703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:2">
       <c r="A334" t="s">
         <v>334</v>
       </c>
@@ -4764,7 +4711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:2">
       <c r="A335" t="s">
         <v>335</v>
       </c>
@@ -4772,7 +4719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:2">
       <c r="A336" t="s">
         <v>336</v>
       </c>
@@ -4780,7 +4727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:2">
       <c r="A337" t="s">
         <v>337</v>
       </c>
@@ -4788,7 +4735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:2">
       <c r="A338" t="s">
         <v>338</v>
       </c>
@@ -4796,7 +4743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:2">
       <c r="A339" t="s">
         <v>339</v>
       </c>
@@ -4804,7 +4751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:2">
       <c r="A340" t="s">
         <v>340</v>
       </c>
@@ -4812,7 +4759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:2">
       <c r="A341" t="s">
         <v>341</v>
       </c>
@@ -4820,7 +4767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:2">
       <c r="A342" t="s">
         <v>342</v>
       </c>
@@ -4828,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:2">
       <c r="A343" t="s">
         <v>343</v>
       </c>
@@ -4836,7 +4783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:2">
       <c r="A344" t="s">
         <v>344</v>
       </c>
@@ -4844,7 +4791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:2">
       <c r="A345" t="s">
         <v>345</v>
       </c>
@@ -4852,7 +4799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:2">
       <c r="A346" t="s">
         <v>346</v>
       </c>
@@ -4860,7 +4807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:2">
       <c r="A347" t="s">
         <v>347</v>
       </c>
@@ -4868,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:2">
       <c r="A348" t="s">
         <v>348</v>
       </c>
@@ -4876,7 +4823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:2">
       <c r="A349" t="s">
         <v>349</v>
       </c>
@@ -4884,7 +4831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:2">
       <c r="A350" t="s">
         <v>350</v>
       </c>
@@ -4892,7 +4839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:2">
       <c r="A351" t="s">
         <v>351</v>
       </c>
@@ -4900,7 +4847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:2">
       <c r="A352" t="s">
         <v>352</v>
       </c>
@@ -4908,7 +4855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:2">
       <c r="A353" t="s">
         <v>353</v>
       </c>
@@ -4916,7 +4863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:2">
       <c r="A354" t="s">
         <v>354</v>
       </c>
@@ -4924,7 +4871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:2">
       <c r="A355" t="s">
         <v>355</v>
       </c>
@@ -4932,7 +4879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:2">
       <c r="A356" t="s">
         <v>356</v>
       </c>
@@ -4940,7 +4887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:2">
       <c r="A357" t="s">
         <v>357</v>
       </c>
@@ -4948,7 +4895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:2">
       <c r="A358" t="s">
         <v>358</v>
       </c>
@@ -4956,7 +4903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:2">
       <c r="A359" t="s">
         <v>359</v>
       </c>
@@ -4964,7 +4911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:2">
       <c r="A360" t="s">
         <v>360</v>
       </c>
@@ -4972,7 +4919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:2">
       <c r="A361" t="s">
         <v>361</v>
       </c>
@@ -4980,7 +4927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:2">
       <c r="A362" t="s">
         <v>362</v>
       </c>
@@ -4988,7 +4935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:2">
       <c r="A363" t="s">
         <v>363</v>
       </c>
@@ -4996,7 +4943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:2">
       <c r="A364" t="s">
         <v>364</v>
       </c>
@@ -5004,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:2">
       <c r="A365" t="s">
         <v>365</v>
       </c>
@@ -5012,7 +4959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:2">
       <c r="A366" t="s">
         <v>366</v>
       </c>
@@ -5020,7 +4967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:2">
       <c r="A367" t="s">
         <v>367</v>
       </c>
@@ -5028,7 +4975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:2">
       <c r="A368" t="s">
         <v>368</v>
       </c>
@@ -5036,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:2">
       <c r="A369" t="s">
         <v>369</v>
       </c>
@@ -5044,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:2">
       <c r="A370" t="s">
         <v>370</v>
       </c>
@@ -5052,7 +4999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:2">
       <c r="A371" t="s">
         <v>371</v>
       </c>
@@ -5060,7 +5007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:2">
       <c r="A372" t="s">
         <v>372</v>
       </c>
@@ -5068,7 +5015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:2">
       <c r="A373" t="s">
         <v>373</v>
       </c>
@@ -5076,7 +5023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:2">
       <c r="A374" t="s">
         <v>374</v>
       </c>
@@ -5084,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:2">
       <c r="A375" t="s">
         <v>375</v>
       </c>
@@ -5092,7 +5039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:2">
       <c r="A376" t="s">
         <v>376</v>
       </c>
@@ -5100,7 +5047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:2">
       <c r="A377" t="s">
         <v>377</v>
       </c>
@@ -5108,7 +5055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:2">
       <c r="A378" t="s">
         <v>378</v>
       </c>
@@ -5116,7 +5063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:2">
       <c r="A379" t="s">
         <v>379</v>
       </c>
@@ -5124,7 +5071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:2">
       <c r="A380" t="s">
         <v>380</v>
       </c>
@@ -5132,7 +5079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:2">
       <c r="A381" t="s">
         <v>381</v>
       </c>
@@ -5140,7 +5087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:2">
       <c r="A382" t="s">
         <v>382</v>
       </c>
@@ -5148,7 +5095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:2">
       <c r="A383" t="s">
         <v>383</v>
       </c>
@@ -5156,7 +5103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:2">
       <c r="A384" t="s">
         <v>384</v>
       </c>
@@ -5164,7 +5111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:2">
       <c r="A385" t="s">
         <v>385</v>
       </c>
@@ -5172,7 +5119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:2">
       <c r="A386" t="s">
         <v>386</v>
       </c>
@@ -5180,7 +5127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:2">
       <c r="A387" t="s">
         <v>387</v>
       </c>
@@ -5188,7 +5135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:2">
       <c r="A388" t="s">
         <v>388</v>
       </c>
@@ -5196,7 +5143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:2">
       <c r="A389" t="s">
         <v>389</v>
       </c>
@@ -5204,7 +5151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:2">
       <c r="A390" t="s">
         <v>390</v>
       </c>
@@ -5212,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:2">
       <c r="A391" t="s">
         <v>391</v>
       </c>
@@ -5220,7 +5167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:2">
       <c r="A392" t="s">
         <v>392</v>
       </c>
@@ -5228,7 +5175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:2">
       <c r="A393" t="s">
         <v>393</v>
       </c>
@@ -5236,7 +5183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:2">
       <c r="A394" t="s">
         <v>394</v>
       </c>
@@ -5244,7 +5191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:2">
       <c r="A395" t="s">
         <v>395</v>
       </c>
@@ -5252,7 +5199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:2">
       <c r="A396" t="s">
         <v>396</v>
       </c>
@@ -5260,7 +5207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:2">
       <c r="A397" t="s">
         <v>397</v>
       </c>
@@ -5268,7 +5215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:2">
       <c r="A398" t="s">
         <v>398</v>
       </c>
@@ -5276,7 +5223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:2">
       <c r="A399" t="s">
         <v>399</v>
       </c>
@@ -5284,7 +5231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:2">
       <c r="A400" t="s">
         <v>400</v>
       </c>
@@ -5292,7 +5239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:2">
       <c r="A401" t="s">
         <v>401</v>
       </c>
@@ -5300,7 +5247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:2">
       <c r="A402" t="s">
         <v>402</v>
       </c>
@@ -5308,7 +5255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:2">
       <c r="A403" t="s">
         <v>403</v>
       </c>
@@ -5316,7 +5263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:2">
       <c r="A404" t="s">
         <v>404</v>
       </c>
@@ -5324,7 +5271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:2">
       <c r="A405" t="s">
         <v>405</v>
       </c>
@@ -5332,7 +5279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:2">
       <c r="A406" t="s">
         <v>406</v>
       </c>
@@ -5340,7 +5287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:2">
       <c r="A407" t="s">
         <v>407</v>
       </c>
@@ -5348,7 +5295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:2">
       <c r="A408" t="s">
         <v>408</v>
       </c>
@@ -5356,7 +5303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:2">
       <c r="A409" t="s">
         <v>409</v>
       </c>
@@ -5364,7 +5311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:2">
       <c r="A410" t="s">
         <v>410</v>
       </c>
@@ -5372,7 +5319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:2">
       <c r="A411" t="s">
         <v>411</v>
       </c>
@@ -5380,7 +5327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:2">
       <c r="A412" t="s">
         <v>412</v>
       </c>
@@ -5388,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:2">
       <c r="A413" t="s">
         <v>413</v>
       </c>
@@ -5396,7 +5343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:2">
       <c r="A414" t="s">
         <v>414</v>
       </c>
@@ -5404,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:2">
       <c r="A415" t="s">
         <v>415</v>
       </c>
@@ -5412,7 +5359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:2">
       <c r="A416" t="s">
         <v>416</v>
       </c>
@@ -5420,7 +5367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:2">
       <c r="A417" t="s">
         <v>417</v>
       </c>
@@ -5428,7 +5375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:2">
       <c r="A418" t="s">
         <v>418</v>
       </c>
@@ -5436,7 +5383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:2">
       <c r="A419" t="s">
         <v>419</v>
       </c>
@@ -5444,7 +5391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:2">
       <c r="A420" t="s">
         <v>420</v>
       </c>
@@ -5452,7 +5399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:2">
       <c r="A421" t="s">
         <v>421</v>
       </c>
@@ -5460,7 +5407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:2">
       <c r="A422" t="s">
         <v>422</v>
       </c>
@@ -5468,7 +5415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:2">
       <c r="A423" t="s">
         <v>423</v>
       </c>
@@ -5476,7 +5423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:2">
       <c r="A424" t="s">
         <v>424</v>
       </c>
@@ -5484,7 +5431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:2">
       <c r="A425" t="s">
         <v>425</v>
       </c>
@@ -5492,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:2">
       <c r="A426" t="s">
         <v>426</v>
       </c>
@@ -5500,7 +5447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:2">
       <c r="A427" t="s">
         <v>427</v>
       </c>
@@ -5508,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:2">
       <c r="A428" t="s">
         <v>428</v>
       </c>
@@ -5516,7 +5463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:2">
       <c r="A429" t="s">
         <v>429</v>
       </c>
@@ -5524,7 +5471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:2">
       <c r="A430" t="s">
         <v>430</v>
       </c>
@@ -5532,7 +5479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:2">
       <c r="A431" t="s">
         <v>431</v>
       </c>
@@ -5540,7 +5487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:2">
       <c r="A432" t="s">
         <v>432</v>
       </c>
@@ -5548,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:2">
       <c r="A433" t="s">
         <v>433</v>
       </c>
@@ -5556,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:2">
       <c r="A434" t="s">
         <v>434</v>
       </c>
@@ -5564,7 +5511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:2">
       <c r="A435" t="s">
         <v>435</v>
       </c>
@@ -5572,7 +5519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:2">
       <c r="A436" t="s">
         <v>436</v>
       </c>
@@ -5580,7 +5527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:2">
       <c r="A437" t="s">
         <v>437</v>
       </c>
@@ -5588,7 +5535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:2">
       <c r="A438" t="s">
         <v>438</v>
       </c>
@@ -5596,7 +5543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:2">
       <c r="A439" t="s">
         <v>439</v>
       </c>
@@ -5604,7 +5551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:2">
       <c r="A440" t="s">
         <v>440</v>
       </c>
@@ -5612,7 +5559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:2">
       <c r="A441" t="s">
         <v>441</v>
       </c>
@@ -5620,7 +5567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:2">
       <c r="A442" t="s">
         <v>442</v>
       </c>
@@ -5628,7 +5575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:2">
       <c r="A443" t="s">
         <v>443</v>
       </c>
@@ -5636,7 +5583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:2">
       <c r="A444" t="s">
         <v>444</v>
       </c>
@@ -5644,7 +5591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:2">
       <c r="A445" t="s">
         <v>445</v>
       </c>
@@ -5652,7 +5599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:2">
       <c r="A446" t="s">
         <v>446</v>
       </c>
@@ -5660,7 +5607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:2">
       <c r="A447" t="s">
         <v>447</v>
       </c>
@@ -5668,7 +5615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:2">
       <c r="A448" t="s">
         <v>448</v>
       </c>
@@ -5676,7 +5623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:2">
       <c r="A449" t="s">
         <v>449</v>
       </c>
@@ -5684,7 +5631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:2">
       <c r="A450" t="s">
         <v>450</v>
       </c>
@@ -5692,7 +5639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:2">
       <c r="A451" t="s">
         <v>451</v>
       </c>
@@ -5700,7 +5647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:2">
       <c r="A452" t="s">
         <v>452</v>
       </c>
@@ -5708,7 +5655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:2">
       <c r="A453" t="s">
         <v>453</v>
       </c>
@@ -5716,7 +5663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:2">
       <c r="A454" t="s">
         <v>454</v>
       </c>
@@ -5724,7 +5671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:2">
       <c r="A455" t="s">
         <v>455</v>
       </c>
@@ -5732,7 +5679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:2">
       <c r="A456" t="s">
         <v>456</v>
       </c>
@@ -5740,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:2">
       <c r="A457" t="s">
         <v>457</v>
       </c>
@@ -5748,7 +5695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:2">
       <c r="A458" t="s">
         <v>458</v>
       </c>
@@ -5756,7 +5703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:2">
       <c r="A459" t="s">
         <v>459</v>
       </c>
@@ -5764,7 +5711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:2">
       <c r="A460" t="s">
         <v>460</v>
       </c>
@@ -5772,7 +5719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:2">
       <c r="A461" t="s">
         <v>461</v>
       </c>
@@ -5780,7 +5727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:2">
       <c r="A462" t="s">
         <v>462</v>
       </c>
@@ -5788,7 +5735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:2">
       <c r="A463" t="s">
         <v>463</v>
       </c>
@@ -5796,7 +5743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:2">
       <c r="A464" t="s">
         <v>464</v>
       </c>
@@ -5804,7 +5751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:2">
       <c r="A465" t="s">
         <v>465</v>
       </c>
@@ -5812,7 +5759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:2">
       <c r="A466" t="s">
         <v>466</v>
       </c>
@@ -5820,7 +5767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:2">
       <c r="A467" t="s">
         <v>467</v>
       </c>
@@ -5828,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:2">
       <c r="A468" t="s">
         <v>468</v>
       </c>
@@ -5836,7 +5783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:2">
       <c r="A469" t="s">
         <v>469</v>
       </c>
@@ -5844,7 +5791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:2">
       <c r="A470" t="s">
         <v>470</v>
       </c>
@@ -5852,7 +5799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:2">
       <c r="A471" t="s">
         <v>471</v>
       </c>
@@ -5860,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:2">
       <c r="A472" t="s">
         <v>472</v>
       </c>
@@ -5868,7 +5815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:2">
       <c r="A473" t="s">
         <v>473</v>
       </c>
@@ -5876,7 +5823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:2">
       <c r="A474" t="s">
         <v>474</v>
       </c>
@@ -5884,7 +5831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:2">
       <c r="A475" t="s">
         <v>475</v>
       </c>
@@ -5892,7 +5839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:2">
       <c r="A476" t="s">
         <v>476</v>
       </c>
@@ -5900,7 +5847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:2">
       <c r="A477" t="s">
         <v>477</v>
       </c>
@@ -5908,7 +5855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:2">
       <c r="A478" t="s">
         <v>478</v>
       </c>
@@ -5916,7 +5863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:2">
       <c r="A479" t="s">
         <v>479</v>
       </c>
@@ -5924,7 +5871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:2">
       <c r="A480" t="s">
         <v>480</v>
       </c>
@@ -5932,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:2">
       <c r="A481" t="s">
         <v>481</v>
       </c>
@@ -5940,7 +5887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:2">
       <c r="A482" t="s">
         <v>482</v>
       </c>
@@ -5948,7 +5895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:2">
       <c r="A483" t="s">
         <v>483</v>
       </c>
@@ -5956,7 +5903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:2">
       <c r="A484" t="s">
         <v>484</v>
       </c>
@@ -5964,7 +5911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:2">
       <c r="A485" t="s">
         <v>485</v>
       </c>
@@ -5972,7 +5919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:2">
       <c r="A486" t="s">
         <v>486</v>
       </c>
@@ -5980,7 +5927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:2">
       <c r="A487" t="s">
         <v>487</v>
       </c>
@@ -5988,7 +5935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:2">
       <c r="A488" t="s">
         <v>488</v>
       </c>
@@ -5996,7 +5943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:2">
       <c r="A489" t="s">
         <v>489</v>
       </c>
@@ -6004,7 +5951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:2">
       <c r="A490" t="s">
         <v>490</v>
       </c>
@@ -6012,7 +5959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:2">
       <c r="A491" t="s">
         <v>491</v>
       </c>
@@ -6020,7 +5967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:2">
       <c r="A492" t="s">
         <v>492</v>
       </c>
@@ -6028,7 +5975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:2">
       <c r="A493" t="s">
         <v>493</v>
       </c>
@@ -6036,7 +5983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:2">
       <c r="A494" t="s">
         <v>494</v>
       </c>
@@ -6044,7 +5991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:2">
       <c r="A495" t="s">
         <v>495</v>
       </c>
@@ -6052,7 +5999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:2">
       <c r="A496" t="s">
         <v>496</v>
       </c>
@@ -6060,7 +6007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:2">
       <c r="A497" t="s">
         <v>497</v>
       </c>
@@ -6068,7 +6015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:2">
       <c r="A498" t="s">
         <v>498</v>
       </c>
@@ -6076,7 +6023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:2">
       <c r="A499" t="s">
         <v>499</v>
       </c>
@@ -6084,7 +6031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:2">
       <c r="A500" t="s">
         <v>500</v>
       </c>
@@ -6092,7 +6039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:2">
       <c r="A501" t="s">
         <v>501</v>
       </c>
@@ -6100,7 +6047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:2">
       <c r="A502" t="s">
         <v>502</v>
       </c>
@@ -6108,7 +6055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:2">
       <c r="A503" t="s">
         <v>503</v>
       </c>
@@ -6116,7 +6063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:2">
       <c r="A504" t="s">
         <v>504</v>
       </c>
@@ -6124,7 +6071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:2">
       <c r="A505" t="s">
         <v>505</v>
       </c>
@@ -6132,7 +6079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:2">
       <c r="A506" t="s">
         <v>506</v>
       </c>
@@ -6140,7 +6087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:2">
       <c r="A507" t="s">
         <v>507</v>
       </c>
@@ -6148,7 +6095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:2">
       <c r="A508" t="s">
         <v>508</v>
       </c>
@@ -6156,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:2">
       <c r="A509" t="s">
         <v>509</v>
       </c>
@@ -6164,7 +6111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:2">
       <c r="A510" t="s">
         <v>510</v>
       </c>
@@ -6172,7 +6119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:2">
       <c r="A511" t="s">
         <v>511</v>
       </c>
@@ -6180,7 +6127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:2">
       <c r="A512" t="s">
         <v>512</v>
       </c>
@@ -6188,7 +6135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:2">
       <c r="A513" t="s">
         <v>513</v>
       </c>
@@ -6196,7 +6143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:2">
       <c r="A514" t="s">
         <v>514</v>
       </c>
@@ -6204,7 +6151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:2">
       <c r="A515" t="s">
         <v>515</v>
       </c>
@@ -6212,7 +6159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:2">
       <c r="A516" t="s">
         <v>516</v>
       </c>
@@ -6220,7 +6167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:2">
       <c r="A517" t="s">
         <v>517</v>
       </c>
@@ -6228,7 +6175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:2">
       <c r="A518" t="s">
         <v>518</v>
       </c>
@@ -6236,7 +6183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:2">
       <c r="A519" t="s">
         <v>519</v>
       </c>
@@ -6244,7 +6191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:2">
       <c r="A520" t="s">
         <v>520</v>
       </c>
@@ -6252,7 +6199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:2">
       <c r="A521" t="s">
         <v>521</v>
       </c>
@@ -6260,7 +6207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:2">
       <c r="A522" t="s">
         <v>522</v>
       </c>
@@ -6268,7 +6215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:2">
       <c r="A523" t="s">
         <v>523</v>
       </c>
@@ -6276,7 +6223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:2">
       <c r="A524" t="s">
         <v>524</v>
       </c>
@@ -6284,7 +6231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:2">
       <c r="A525" t="s">
         <v>525</v>
       </c>
@@ -6292,7 +6239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:2">
       <c r="A526" t="s">
         <v>526</v>
       </c>
@@ -6300,7 +6247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:2">
       <c r="A527" t="s">
         <v>527</v>
       </c>
@@ -6308,7 +6255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:2">
       <c r="A528" t="s">
         <v>528</v>
       </c>
@@ -6316,7 +6263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:2">
       <c r="A529" t="s">
         <v>529</v>
       </c>
@@ -6324,7 +6271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:2">
       <c r="A530" t="s">
         <v>530</v>
       </c>
@@ -6332,7 +6279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:2">
       <c r="A531" t="s">
         <v>531</v>
       </c>
@@ -6340,7 +6287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:2">
       <c r="A532" t="s">
         <v>532</v>
       </c>
@@ -6348,7 +6295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:2">
       <c r="A533" t="s">
         <v>533</v>
       </c>
@@ -6356,7 +6303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:2">
       <c r="A534" t="s">
         <v>534</v>
       </c>
@@ -6364,7 +6311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:2">
       <c r="A535" t="s">
         <v>535</v>
       </c>
@@ -6372,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:2">
       <c r="A536" t="s">
         <v>536</v>
       </c>
@@ -6380,7 +6327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:2">
       <c r="A537" t="s">
         <v>537</v>
       </c>
@@ -6388,7 +6335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:2">
       <c r="A538" t="s">
         <v>538</v>
       </c>
@@ -6396,7 +6343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:2">
       <c r="A539" t="s">
         <v>539</v>
       </c>
@@ -6404,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:2">
       <c r="A540" t="s">
         <v>540</v>
       </c>
@@ -6412,7 +6359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:2">
       <c r="A541" t="s">
         <v>541</v>
       </c>
@@ -6420,7 +6367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:2">
       <c r="A542" t="s">
         <v>542</v>
       </c>
@@ -6428,7 +6375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:2">
       <c r="A543" t="s">
         <v>543</v>
       </c>
@@ -6436,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:2">
       <c r="A544" t="s">
         <v>544</v>
       </c>
@@ -6444,7 +6391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:2">
       <c r="A545" t="s">
         <v>545</v>
       </c>
@@ -6452,7 +6399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:2">
       <c r="A546" t="s">
         <v>546</v>
       </c>
@@ -6460,7 +6407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:2">
       <c r="A547" t="s">
         <v>547</v>
       </c>
@@ -6468,7 +6415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:2">
       <c r="A548" t="s">
         <v>548</v>
       </c>
@@ -6476,7 +6423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:2">
       <c r="A549" t="s">
         <v>549</v>
       </c>
@@ -6484,7 +6431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:2">
       <c r="A550" t="s">
         <v>550</v>
       </c>
@@ -6492,7 +6439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:2">
       <c r="A551" t="s">
         <v>551</v>
       </c>
@@ -6500,7 +6447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:2">
       <c r="A552" t="s">
         <v>552</v>
       </c>
@@ -6508,7 +6455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:2">
       <c r="A553" t="s">
         <v>553</v>
       </c>
@@ -6516,7 +6463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:2">
       <c r="A554" t="s">
         <v>554</v>
       </c>
